--- a/selenium-tests/selenium-web-report.xlsx
+++ b/selenium-tests/selenium-web-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="885">
   <si>
     <t>Metric</t>
   </si>
@@ -62,7 +62,7 @@
     <t>EXECUTION TIME</t>
   </si>
   <si>
-    <t>0.00 seconds</t>
+    <t>64.62 seconds</t>
   </si>
   <si>
     <t>Automated headless Chrome runner</t>
@@ -71,7 +71,7 @@
     <t>EXECUTION TIMESTAMP</t>
   </si>
   <si>
-    <t>7/8/2026, 9:49:34 am</t>
+    <t>7/8/2026, 10:47:52 am</t>
   </si>
   <si>
     <t>CI/CD Pipeline Run</t>
@@ -176,7 +176,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-08-07T04:19:34.654Z</t>
+    <t>2026-08-07T05:17:52.499Z</t>
   </si>
   <si>
     <t>TC-WEB-002</t>
@@ -188,7 +188,7 @@
     <t>username='user_2@test.com', auth_type='password'</t>
   </si>
   <si>
-    <t>2026-08-07T04:19:34.656Z</t>
+    <t>2026-08-07T05:17:52.501Z</t>
   </si>
   <si>
     <t>TC-WEB-003</t>
@@ -551,6 +551,9 @@
     <t>viewport='1920x1080', theme='dark', hero_index=7</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:52.502Z</t>
+  </si>
+  <si>
     <t>TC-WEB-043</t>
   </si>
   <si>
@@ -980,9 +983,6 @@
     <t>Destination Filter Tag &amp; Search Bar Interaction #22 (Nature)</t>
   </si>
   <si>
-    <t>2026-08-07T04:19:34.657Z</t>
-  </si>
-  <si>
     <t>TC-WEB-093</t>
   </si>
   <si>
@@ -1244,6 +1244,9 @@
     <t>AI Trip Planner Multi-Step Form Submission #17 (4 Days)</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:52.503Z</t>
+  </si>
+  <si>
     <t>TC-WEB-128</t>
   </si>
   <si>
@@ -2114,6 +2117,9 @@
     <t>Payment processed: Booking Ref #TN-2026-0033 issued</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:52.504Z</t>
+  </si>
+  <si>
     <t>TC-WEB-219</t>
   </si>
   <si>
@@ -2607,9 +2613,6 @@
   </si>
   <si>
     <t>Admin Analytics Chart Rendering &amp; Table Sorting #21</t>
-  </si>
-  <si>
-    <t>2026-08-07T04:19:34.658Z</t>
   </si>
   <si>
     <t>TC-WEB-292</t>
@@ -4681,12 +4684,12 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B44" t="s">
         <v>155</v>
@@ -4695,10 +4698,10 @@
         <v>156</v>
       </c>
       <c r="D44" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F44" t="s">
         <v>159</v>
@@ -4713,12 +4716,12 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B45" t="s">
         <v>155</v>
@@ -4727,10 +4730,10 @@
         <v>156</v>
       </c>
       <c r="D45" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E45" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F45" t="s">
         <v>159</v>
@@ -4745,12 +4748,12 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B46" t="s">
         <v>155</v>
@@ -4759,10 +4762,10 @@
         <v>156</v>
       </c>
       <c r="D46" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E46" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F46" t="s">
         <v>159</v>
@@ -4777,12 +4780,12 @@
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B47" t="s">
         <v>155</v>
@@ -4791,10 +4794,10 @@
         <v>156</v>
       </c>
       <c r="D47" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E47" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F47" t="s">
         <v>159</v>
@@ -4809,12 +4812,12 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B48" t="s">
         <v>155</v>
@@ -4823,10 +4826,10 @@
         <v>156</v>
       </c>
       <c r="D48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E48" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F48" t="s">
         <v>159</v>
@@ -4841,12 +4844,12 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B49" t="s">
         <v>155</v>
@@ -4855,10 +4858,10 @@
         <v>156</v>
       </c>
       <c r="D49" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F49" t="s">
         <v>159</v>
@@ -4873,12 +4876,12 @@
         <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B50" t="s">
         <v>155</v>
@@ -4887,10 +4890,10 @@
         <v>156</v>
       </c>
       <c r="D50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F50" t="s">
         <v>159</v>
@@ -4905,12 +4908,12 @@
         <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B51" t="s">
         <v>155</v>
@@ -4919,10 +4922,10 @@
         <v>156</v>
       </c>
       <c r="D51" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E51" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F51" t="s">
         <v>159</v>
@@ -4937,12 +4940,12 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B52" t="s">
         <v>155</v>
@@ -4951,10 +4954,10 @@
         <v>156</v>
       </c>
       <c r="D52" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E52" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F52" t="s">
         <v>159</v>
@@ -4969,12 +4972,12 @@
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B53" t="s">
         <v>155</v>
@@ -4983,10 +4986,10 @@
         <v>156</v>
       </c>
       <c r="D53" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E53" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F53" t="s">
         <v>159</v>
@@ -5001,12 +5004,12 @@
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B54" t="s">
         <v>155</v>
@@ -5015,10 +5018,10 @@
         <v>156</v>
       </c>
       <c r="D54" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E54" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F54" t="s">
         <v>159</v>
@@ -5033,12 +5036,12 @@
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B55" t="s">
         <v>155</v>
@@ -5047,10 +5050,10 @@
         <v>156</v>
       </c>
       <c r="D55" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E55" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F55" t="s">
         <v>159</v>
@@ -5065,12 +5068,12 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B56" t="s">
         <v>155</v>
@@ -5079,10 +5082,10 @@
         <v>156</v>
       </c>
       <c r="D56" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F56" t="s">
         <v>159</v>
@@ -5097,12 +5100,12 @@
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B57" t="s">
         <v>155</v>
@@ -5111,10 +5114,10 @@
         <v>156</v>
       </c>
       <c r="D57" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E57" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F57" t="s">
         <v>159</v>
@@ -5129,12 +5132,12 @@
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B58" t="s">
         <v>155</v>
@@ -5143,10 +5146,10 @@
         <v>156</v>
       </c>
       <c r="D58" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E58" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F58" t="s">
         <v>159</v>
@@ -5161,12 +5164,12 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B59" t="s">
         <v>155</v>
@@ -5175,10 +5178,10 @@
         <v>156</v>
       </c>
       <c r="D59" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E59" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F59" t="s">
         <v>159</v>
@@ -5193,12 +5196,12 @@
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B60" t="s">
         <v>155</v>
@@ -5207,10 +5210,10 @@
         <v>156</v>
       </c>
       <c r="D60" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E60" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F60" t="s">
         <v>159</v>
@@ -5225,12 +5228,12 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B61" t="s">
         <v>155</v>
@@ -5239,10 +5242,10 @@
         <v>156</v>
       </c>
       <c r="D61" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E61" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F61" t="s">
         <v>159</v>
@@ -5257,12 +5260,12 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B62" t="s">
         <v>155</v>
@@ -5271,10 +5274,10 @@
         <v>156</v>
       </c>
       <c r="D62" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E62" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F62" t="s">
         <v>159</v>
@@ -5289,12 +5292,12 @@
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B63" t="s">
         <v>155</v>
@@ -5303,10 +5306,10 @@
         <v>156</v>
       </c>
       <c r="D63" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E63" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F63" t="s">
         <v>159</v>
@@ -5321,12 +5324,12 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B64" t="s">
         <v>155</v>
@@ -5335,10 +5338,10 @@
         <v>156</v>
       </c>
       <c r="D64" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E64" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F64" t="s">
         <v>159</v>
@@ -5353,12 +5356,12 @@
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B65" t="s">
         <v>155</v>
@@ -5367,10 +5370,10 @@
         <v>156</v>
       </c>
       <c r="D65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E65" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F65" t="s">
         <v>159</v>
@@ -5385,12 +5388,12 @@
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B66" t="s">
         <v>155</v>
@@ -5399,10 +5402,10 @@
         <v>156</v>
       </c>
       <c r="D66" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F66" t="s">
         <v>159</v>
@@ -5417,12 +5420,12 @@
         <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B67" t="s">
         <v>155</v>
@@ -5431,10 +5434,10 @@
         <v>156</v>
       </c>
       <c r="D67" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E67" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F67" t="s">
         <v>159</v>
@@ -5449,12 +5452,12 @@
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B68" t="s">
         <v>155</v>
@@ -5463,10 +5466,10 @@
         <v>156</v>
       </c>
       <c r="D68" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E68" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F68" t="s">
         <v>159</v>
@@ -5481,12 +5484,12 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B69" t="s">
         <v>155</v>
@@ -5495,10 +5498,10 @@
         <v>156</v>
       </c>
       <c r="D69" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E69" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F69" t="s">
         <v>159</v>
@@ -5513,12 +5516,12 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B70" t="s">
         <v>155</v>
@@ -5527,10 +5530,10 @@
         <v>156</v>
       </c>
       <c r="D70" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E70" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F70" t="s">
         <v>159</v>
@@ -5545,12 +5548,12 @@
         <v>1</v>
       </c>
       <c r="J70" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B71" t="s">
         <v>155</v>
@@ -5559,10 +5562,10 @@
         <v>156</v>
       </c>
       <c r="D71" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E71" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F71" t="s">
         <v>159</v>
@@ -5577,30 +5580,30 @@
         <v>1</v>
       </c>
       <c r="J71" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B72" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C72" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E72" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>53</v>
@@ -5609,31 +5612,31 @@
         <v>1</v>
       </c>
       <c r="J72" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>271</v>
+      </c>
+      <c r="B73" t="s">
+        <v>265</v>
+      </c>
+      <c r="C73" t="s">
+        <v>266</v>
+      </c>
+      <c r="D73" t="s">
+        <v>272</v>
+      </c>
+      <c r="E73" t="s">
+        <v>273</v>
+      </c>
+      <c r="F73" t="s">
+        <v>274</v>
+      </c>
+      <c r="G73" t="s">
         <v>270</v>
       </c>
-      <c r="B73" t="s">
-        <v>264</v>
-      </c>
-      <c r="C73" t="s">
-        <v>265</v>
-      </c>
-      <c r="D73" t="s">
-        <v>271</v>
-      </c>
-      <c r="E73" t="s">
-        <v>272</v>
-      </c>
-      <c r="F73" t="s">
-        <v>273</v>
-      </c>
-      <c r="G73" t="s">
-        <v>269</v>
-      </c>
       <c r="H73" s="3" t="s">
         <v>53</v>
       </c>
@@ -5641,30 +5644,30 @@
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B74" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C74" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D74" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E74" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F74" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G74" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>53</v>
@@ -5673,30 +5676,30 @@
         <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B75" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C75" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D75" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E75" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F75" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G75" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>53</v>
@@ -5705,30 +5708,30 @@
         <v>1</v>
       </c>
       <c r="J75" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C76" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D76" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E76" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F76" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G76" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>53</v>
@@ -5737,30 +5740,30 @@
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B77" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C77" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D77" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E77" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F77" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G77" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>53</v>
@@ -5769,30 +5772,30 @@
         <v>1</v>
       </c>
       <c r="J77" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B78" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C78" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D78" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E78" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F78" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G78" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>53</v>
@@ -5801,30 +5804,30 @@
         <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B79" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C79" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D79" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E79" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F79" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G79" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>53</v>
@@ -5833,30 +5836,30 @@
         <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B80" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C80" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D80" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E80" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F80" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G80" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>53</v>
@@ -5865,30 +5868,30 @@
         <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B81" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C81" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D81" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E81" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F81" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G81" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>53</v>
@@ -5897,30 +5900,30 @@
         <v>1</v>
       </c>
       <c r="J81" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B82" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C82" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D82" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E82" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F82" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G82" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>53</v>
@@ -5929,30 +5932,30 @@
         <v>1</v>
       </c>
       <c r="J82" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B83" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C83" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D83" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E83" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F83" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G83" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>53</v>
@@ -5961,30 +5964,30 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B84" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C84" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D84" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G84" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>53</v>
@@ -5993,30 +5996,30 @@
         <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B85" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C85" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D85" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E85" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F85" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G85" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>53</v>
@@ -6025,30 +6028,30 @@
         <v>1</v>
       </c>
       <c r="J85" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B86" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C86" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D86" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E86" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F86" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G86" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>53</v>
@@ -6057,30 +6060,30 @@
         <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B87" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C87" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D87" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E87" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F87" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G87" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>53</v>
@@ -6089,30 +6092,30 @@
         <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B88" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C88" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D88" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E88" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F88" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G88" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>53</v>
@@ -6121,30 +6124,30 @@
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B89" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C89" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D89" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E89" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F89" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G89" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>53</v>
@@ -6153,30 +6156,30 @@
         <v>1</v>
       </c>
       <c r="J89" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B90" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C90" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D90" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E90" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G90" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>53</v>
@@ -6185,30 +6188,30 @@
         <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B91" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C91" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D91" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E91" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F91" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G91" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>53</v>
@@ -6217,30 +6220,30 @@
         <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B92" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C92" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D92" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E92" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F92" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G92" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>53</v>
@@ -6249,30 +6252,30 @@
         <v>1</v>
       </c>
       <c r="J92" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B93" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C93" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D93" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E93" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F93" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G93" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>53</v>
@@ -6281,7 +6284,7 @@
         <v>1</v>
       </c>
       <c r="J93" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -6289,22 +6292,22 @@
         <v>323</v>
       </c>
       <c r="B94" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C94" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D94" t="s">
         <v>324</v>
       </c>
       <c r="E94" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F94" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G94" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>53</v>
@@ -6313,7 +6316,7 @@
         <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -6321,22 +6324,22 @@
         <v>325</v>
       </c>
       <c r="B95" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C95" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D95" t="s">
         <v>326</v>
       </c>
       <c r="E95" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F95" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>53</v>
@@ -6345,7 +6348,7 @@
         <v>1</v>
       </c>
       <c r="J95" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -6353,22 +6356,22 @@
         <v>327</v>
       </c>
       <c r="B96" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C96" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D96" t="s">
         <v>328</v>
       </c>
       <c r="E96" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F96" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G96" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>53</v>
@@ -6377,7 +6380,7 @@
         <v>1</v>
       </c>
       <c r="J96" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -6385,22 +6388,22 @@
         <v>329</v>
       </c>
       <c r="B97" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C97" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D97" t="s">
         <v>330</v>
       </c>
       <c r="E97" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F97" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G97" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>53</v>
@@ -6409,7 +6412,7 @@
         <v>1</v>
       </c>
       <c r="J97" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -6417,22 +6420,22 @@
         <v>331</v>
       </c>
       <c r="B98" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C98" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D98" t="s">
         <v>332</v>
       </c>
       <c r="E98" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F98" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G98" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>53</v>
@@ -6441,7 +6444,7 @@
         <v>1</v>
       </c>
       <c r="J98" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -6449,22 +6452,22 @@
         <v>333</v>
       </c>
       <c r="B99" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C99" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D99" t="s">
         <v>334</v>
       </c>
       <c r="E99" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F99" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G99" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>53</v>
@@ -6473,7 +6476,7 @@
         <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -6481,22 +6484,22 @@
         <v>335</v>
       </c>
       <c r="B100" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C100" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D100" t="s">
         <v>336</v>
       </c>
       <c r="E100" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F100" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>53</v>
@@ -6505,7 +6508,7 @@
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -6513,22 +6516,22 @@
         <v>337</v>
       </c>
       <c r="B101" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C101" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D101" t="s">
         <v>338</v>
       </c>
       <c r="E101" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F101" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G101" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>53</v>
@@ -6537,7 +6540,7 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -6545,22 +6548,22 @@
         <v>339</v>
       </c>
       <c r="B102" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C102" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D102" t="s">
         <v>340</v>
       </c>
       <c r="E102" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F102" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G102" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>53</v>
@@ -6569,7 +6572,7 @@
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -6577,22 +6580,22 @@
         <v>341</v>
       </c>
       <c r="B103" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C103" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D103" t="s">
         <v>342</v>
       </c>
       <c r="E103" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F103" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>53</v>
@@ -6601,7 +6604,7 @@
         <v>1</v>
       </c>
       <c r="J103" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -6609,22 +6612,22 @@
         <v>343</v>
       </c>
       <c r="B104" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C104" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D104" t="s">
         <v>344</v>
       </c>
       <c r="E104" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F104" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G104" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>53</v>
@@ -6633,7 +6636,7 @@
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -6641,22 +6644,22 @@
         <v>345</v>
       </c>
       <c r="B105" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C105" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D105" t="s">
         <v>346</v>
       </c>
       <c r="E105" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F105" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G105" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>53</v>
@@ -6665,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -6673,22 +6676,22 @@
         <v>347</v>
       </c>
       <c r="B106" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C106" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D106" t="s">
         <v>348</v>
       </c>
       <c r="E106" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F106" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G106" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>53</v>
@@ -6697,7 +6700,7 @@
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -6705,22 +6708,22 @@
         <v>349</v>
       </c>
       <c r="B107" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C107" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D107" t="s">
         <v>350</v>
       </c>
       <c r="E107" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F107" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G107" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H107" s="3" t="s">
         <v>53</v>
@@ -6729,7 +6732,7 @@
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -6737,22 +6740,22 @@
         <v>351</v>
       </c>
       <c r="B108" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C108" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D108" t="s">
         <v>352</v>
       </c>
       <c r="E108" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F108" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G108" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>53</v>
@@ -6761,7 +6764,7 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -6769,22 +6772,22 @@
         <v>353</v>
       </c>
       <c r="B109" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C109" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D109" t="s">
         <v>354</v>
       </c>
       <c r="E109" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F109" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G109" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>53</v>
@@ -6793,7 +6796,7 @@
         <v>1</v>
       </c>
       <c r="J109" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -6801,22 +6804,22 @@
         <v>355</v>
       </c>
       <c r="B110" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C110" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D110" t="s">
         <v>356</v>
       </c>
       <c r="E110" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F110" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G110" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>53</v>
@@ -6825,7 +6828,7 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -6833,22 +6836,22 @@
         <v>357</v>
       </c>
       <c r="B111" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C111" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D111" t="s">
         <v>358</v>
       </c>
       <c r="E111" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F111" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G111" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>53</v>
@@ -6857,7 +6860,7 @@
         <v>1</v>
       </c>
       <c r="J111" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -6889,7 +6892,7 @@
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -6921,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -6953,7 +6956,7 @@
         <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -6985,7 +6988,7 @@
         <v>1</v>
       </c>
       <c r="J115" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -7017,7 +7020,7 @@
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -7049,7 +7052,7 @@
         <v>1</v>
       </c>
       <c r="J117" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -7081,7 +7084,7 @@
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -7113,7 +7116,7 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -7145,7 +7148,7 @@
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -7177,7 +7180,7 @@
         <v>1</v>
       </c>
       <c r="J121" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -7209,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="J122" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -7241,7 +7244,7 @@
         <v>1</v>
       </c>
       <c r="J123" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -7273,7 +7276,7 @@
         <v>1</v>
       </c>
       <c r="J124" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -7305,7 +7308,7 @@
         <v>1</v>
       </c>
       <c r="J125" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -7337,7 +7340,7 @@
         <v>1</v>
       </c>
       <c r="J126" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -7369,7 +7372,7 @@
         <v>1</v>
       </c>
       <c r="J127" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -7401,12 +7404,12 @@
         <v>1</v>
       </c>
       <c r="J128" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B129" t="s">
         <v>360</v>
@@ -7415,7 +7418,7 @@
         <v>361</v>
       </c>
       <c r="D129" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E129" t="s">
         <v>376</v>
@@ -7433,12 +7436,12 @@
         <v>1</v>
       </c>
       <c r="J129" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B130" t="s">
         <v>360</v>
@@ -7447,7 +7450,7 @@
         <v>361</v>
       </c>
       <c r="D130" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E130" t="s">
         <v>380</v>
@@ -7465,12 +7468,12 @@
         <v>1</v>
       </c>
       <c r="J130" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B131" t="s">
         <v>360</v>
@@ -7479,7 +7482,7 @@
         <v>361</v>
       </c>
       <c r="D131" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E131" t="s">
         <v>384</v>
@@ -7497,12 +7500,12 @@
         <v>1</v>
       </c>
       <c r="J131" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B132" t="s">
         <v>360</v>
@@ -7511,7 +7514,7 @@
         <v>361</v>
       </c>
       <c r="D132" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E132" t="s">
         <v>388</v>
@@ -7529,12 +7532,12 @@
         <v>1</v>
       </c>
       <c r="J132" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B133" t="s">
         <v>360</v>
@@ -7543,7 +7546,7 @@
         <v>361</v>
       </c>
       <c r="D133" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E133" t="s">
         <v>363</v>
@@ -7561,12 +7564,12 @@
         <v>1</v>
       </c>
       <c r="J133" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B134" t="s">
         <v>360</v>
@@ -7575,7 +7578,7 @@
         <v>361</v>
       </c>
       <c r="D134" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E134" t="s">
         <v>368</v>
@@ -7593,12 +7596,12 @@
         <v>1</v>
       </c>
       <c r="J134" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B135" t="s">
         <v>360</v>
@@ -7607,7 +7610,7 @@
         <v>361</v>
       </c>
       <c r="D135" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E135" t="s">
         <v>372</v>
@@ -7625,12 +7628,12 @@
         <v>1</v>
       </c>
       <c r="J135" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B136" t="s">
         <v>360</v>
@@ -7639,7 +7642,7 @@
         <v>361</v>
       </c>
       <c r="D136" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E136" t="s">
         <v>376</v>
@@ -7657,12 +7660,12 @@
         <v>1</v>
       </c>
       <c r="J136" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B137" t="s">
         <v>360</v>
@@ -7671,7 +7674,7 @@
         <v>361</v>
       </c>
       <c r="D137" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E137" t="s">
         <v>380</v>
@@ -7689,12 +7692,12 @@
         <v>1</v>
       </c>
       <c r="J137" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B138" t="s">
         <v>360</v>
@@ -7703,7 +7706,7 @@
         <v>361</v>
       </c>
       <c r="D138" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E138" t="s">
         <v>384</v>
@@ -7721,12 +7724,12 @@
         <v>1</v>
       </c>
       <c r="J138" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B139" t="s">
         <v>360</v>
@@ -7735,7 +7738,7 @@
         <v>361</v>
       </c>
       <c r="D139" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E139" t="s">
         <v>388</v>
@@ -7753,12 +7756,12 @@
         <v>1</v>
       </c>
       <c r="J139" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B140" t="s">
         <v>360</v>
@@ -7767,7 +7770,7 @@
         <v>361</v>
       </c>
       <c r="D140" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E140" t="s">
         <v>363</v>
@@ -7785,12 +7788,12 @@
         <v>1</v>
       </c>
       <c r="J140" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B141" t="s">
         <v>360</v>
@@ -7799,7 +7802,7 @@
         <v>361</v>
       </c>
       <c r="D141" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E141" t="s">
         <v>368</v>
@@ -7817,12 +7820,12 @@
         <v>1</v>
       </c>
       <c r="J141" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B142" t="s">
         <v>360</v>
@@ -7831,7 +7834,7 @@
         <v>361</v>
       </c>
       <c r="D142" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E142" t="s">
         <v>372</v>
@@ -7849,12 +7852,12 @@
         <v>1</v>
       </c>
       <c r="J142" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B143" t="s">
         <v>360</v>
@@ -7863,7 +7866,7 @@
         <v>361</v>
       </c>
       <c r="D143" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E143" t="s">
         <v>376</v>
@@ -7881,12 +7884,12 @@
         <v>1</v>
       </c>
       <c r="J143" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B144" t="s">
         <v>360</v>
@@ -7895,7 +7898,7 @@
         <v>361</v>
       </c>
       <c r="D144" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E144" t="s">
         <v>380</v>
@@ -7913,12 +7916,12 @@
         <v>1</v>
       </c>
       <c r="J144" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B145" t="s">
         <v>360</v>
@@ -7927,7 +7930,7 @@
         <v>361</v>
       </c>
       <c r="D145" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E145" t="s">
         <v>384</v>
@@ -7945,12 +7948,12 @@
         <v>1</v>
       </c>
       <c r="J145" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B146" t="s">
         <v>360</v>
@@ -7959,7 +7962,7 @@
         <v>361</v>
       </c>
       <c r="D146" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E146" t="s">
         <v>388</v>
@@ -7977,12 +7980,12 @@
         <v>1</v>
       </c>
       <c r="J146" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B147" t="s">
         <v>360</v>
@@ -7991,7 +7994,7 @@
         <v>361</v>
       </c>
       <c r="D147" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E147" t="s">
         <v>363</v>
@@ -8009,12 +8012,12 @@
         <v>1</v>
       </c>
       <c r="J147" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B148" t="s">
         <v>360</v>
@@ -8023,7 +8026,7 @@
         <v>361</v>
       </c>
       <c r="D148" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E148" t="s">
         <v>368</v>
@@ -8041,12 +8044,12 @@
         <v>1</v>
       </c>
       <c r="J148" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B149" t="s">
         <v>360</v>
@@ -8055,7 +8058,7 @@
         <v>361</v>
       </c>
       <c r="D149" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E149" t="s">
         <v>372</v>
@@ -8073,12 +8076,12 @@
         <v>1</v>
       </c>
       <c r="J149" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B150" t="s">
         <v>360</v>
@@ -8087,7 +8090,7 @@
         <v>361</v>
       </c>
       <c r="D150" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E150" t="s">
         <v>376</v>
@@ -8105,12 +8108,12 @@
         <v>1</v>
       </c>
       <c r="J150" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B151" t="s">
         <v>360</v>
@@ -8119,7 +8122,7 @@
         <v>361</v>
       </c>
       <c r="D151" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E151" t="s">
         <v>380</v>
@@ -8137,30 +8140,30 @@
         <v>1</v>
       </c>
       <c r="J151" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B152" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C152" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D152" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E152" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F152" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G152" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H152" s="3" t="s">
         <v>53</v>
@@ -8169,31 +8172,31 @@
         <v>1</v>
       </c>
       <c r="J152" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>464</v>
+      </c>
+      <c r="B153" t="s">
+        <v>458</v>
+      </c>
+      <c r="C153" t="s">
+        <v>459</v>
+      </c>
+      <c r="D153" t="s">
+        <v>465</v>
+      </c>
+      <c r="E153" t="s">
+        <v>466</v>
+      </c>
+      <c r="F153" t="s">
+        <v>462</v>
+      </c>
+      <c r="G153" t="s">
         <v>463</v>
       </c>
-      <c r="B153" t="s">
-        <v>457</v>
-      </c>
-      <c r="C153" t="s">
-        <v>458</v>
-      </c>
-      <c r="D153" t="s">
-        <v>464</v>
-      </c>
-      <c r="E153" t="s">
-        <v>465</v>
-      </c>
-      <c r="F153" t="s">
-        <v>461</v>
-      </c>
-      <c r="G153" t="s">
-        <v>462</v>
-      </c>
       <c r="H153" s="3" t="s">
         <v>53</v>
       </c>
@@ -8201,30 +8204,30 @@
         <v>1</v>
       </c>
       <c r="J153" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B154" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C154" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D154" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E154" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F154" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G154" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H154" s="3" t="s">
         <v>53</v>
@@ -8233,30 +8236,30 @@
         <v>1</v>
       </c>
       <c r="J154" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B155" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C155" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D155" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E155" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F155" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G155" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H155" s="3" t="s">
         <v>53</v>
@@ -8265,30 +8268,30 @@
         <v>1</v>
       </c>
       <c r="J155" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B156" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C156" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D156" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E156" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F156" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G156" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H156" s="3" t="s">
         <v>53</v>
@@ -8297,30 +8300,30 @@
         <v>1</v>
       </c>
       <c r="J156" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B157" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C157" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D157" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E157" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F157" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G157" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H157" s="3" t="s">
         <v>53</v>
@@ -8329,30 +8332,30 @@
         <v>1</v>
       </c>
       <c r="J157" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B158" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C158" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D158" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E158" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F158" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G158" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>53</v>
@@ -8361,30 +8364,30 @@
         <v>1</v>
       </c>
       <c r="J158" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B159" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C159" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D159" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E159" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F159" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G159" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H159" s="3" t="s">
         <v>53</v>
@@ -8393,30 +8396,30 @@
         <v>1</v>
       </c>
       <c r="J159" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B160" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C160" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D160" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E160" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F160" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G160" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H160" s="3" t="s">
         <v>53</v>
@@ -8425,30 +8428,30 @@
         <v>1</v>
       </c>
       <c r="J160" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B161" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C161" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D161" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E161" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F161" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G161" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H161" s="3" t="s">
         <v>53</v>
@@ -8457,30 +8460,30 @@
         <v>1</v>
       </c>
       <c r="J161" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B162" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C162" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D162" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E162" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F162" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G162" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H162" s="3" t="s">
         <v>53</v>
@@ -8489,30 +8492,30 @@
         <v>1</v>
       </c>
       <c r="J162" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B163" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C163" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D163" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E163" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F163" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G163" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H163" s="3" t="s">
         <v>53</v>
@@ -8521,30 +8524,30 @@
         <v>1</v>
       </c>
       <c r="J163" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B164" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C164" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D164" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E164" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F164" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G164" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H164" s="3" t="s">
         <v>53</v>
@@ -8553,30 +8556,30 @@
         <v>1</v>
       </c>
       <c r="J164" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B165" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C165" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D165" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E165" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F165" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G165" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H165" s="3" t="s">
         <v>53</v>
@@ -8585,30 +8588,30 @@
         <v>1</v>
       </c>
       <c r="J165" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B166" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C166" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D166" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E166" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F166" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G166" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H166" s="3" t="s">
         <v>53</v>
@@ -8617,30 +8620,30 @@
         <v>1</v>
       </c>
       <c r="J166" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B167" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C167" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D167" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E167" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F167" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G167" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H167" s="3" t="s">
         <v>53</v>
@@ -8649,30 +8652,30 @@
         <v>1</v>
       </c>
       <c r="J167" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B168" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C168" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D168" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E168" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F168" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G168" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H168" s="3" t="s">
         <v>53</v>
@@ -8681,30 +8684,30 @@
         <v>1</v>
       </c>
       <c r="J168" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B169" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C169" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D169" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E169" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F169" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G169" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H169" s="3" t="s">
         <v>53</v>
@@ -8713,30 +8716,30 @@
         <v>1</v>
       </c>
       <c r="J169" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B170" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C170" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D170" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E170" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F170" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G170" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H170" s="3" t="s">
         <v>53</v>
@@ -8745,30 +8748,30 @@
         <v>1</v>
       </c>
       <c r="J170" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B171" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C171" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D171" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E171" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F171" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G171" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H171" s="3" t="s">
         <v>53</v>
@@ -8777,30 +8780,30 @@
         <v>1</v>
       </c>
       <c r="J171" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B172" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C172" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D172" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E172" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F172" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G172" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H172" s="3" t="s">
         <v>53</v>
@@ -8809,30 +8812,30 @@
         <v>1</v>
       </c>
       <c r="J172" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B173" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C173" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D173" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E173" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F173" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G173" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H173" s="3" t="s">
         <v>53</v>
@@ -8841,30 +8844,30 @@
         <v>1</v>
       </c>
       <c r="J173" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B174" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C174" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D174" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E174" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F174" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G174" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H174" s="3" t="s">
         <v>53</v>
@@ -8873,30 +8876,30 @@
         <v>1</v>
       </c>
       <c r="J174" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B175" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C175" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D175" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E175" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F175" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G175" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H175" s="3" t="s">
         <v>53</v>
@@ -8905,30 +8908,30 @@
         <v>1</v>
       </c>
       <c r="J175" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B176" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C176" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D176" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E176" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F176" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G176" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>53</v>
@@ -8937,30 +8940,30 @@
         <v>1</v>
       </c>
       <c r="J176" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B177" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C177" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D177" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E177" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F177" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G177" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>53</v>
@@ -8969,30 +8972,30 @@
         <v>1</v>
       </c>
       <c r="J177" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B178" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C178" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D178" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E178" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F178" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G178" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H178" s="3" t="s">
         <v>53</v>
@@ -9001,30 +9004,30 @@
         <v>1</v>
       </c>
       <c r="J178" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B179" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C179" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D179" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E179" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F179" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G179" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H179" s="3" t="s">
         <v>53</v>
@@ -9033,30 +9036,30 @@
         <v>1</v>
       </c>
       <c r="J179" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B180" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C180" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D180" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E180" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F180" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G180" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>53</v>
@@ -9065,30 +9068,30 @@
         <v>1</v>
       </c>
       <c r="J180" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B181" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C181" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D181" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E181" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F181" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G181" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H181" s="3" t="s">
         <v>53</v>
@@ -9097,30 +9100,30 @@
         <v>1</v>
       </c>
       <c r="J181" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B182" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C182" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D182" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E182" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F182" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G182" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>53</v>
@@ -9129,30 +9132,30 @@
         <v>1</v>
       </c>
       <c r="J182" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B183" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C183" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D183" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E183" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F183" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G183" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H183" s="3" t="s">
         <v>53</v>
@@ -9161,30 +9164,30 @@
         <v>1</v>
       </c>
       <c r="J183" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B184" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C184" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D184" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E184" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F184" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G184" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H184" s="3" t="s">
         <v>53</v>
@@ -9193,30 +9196,30 @@
         <v>1</v>
       </c>
       <c r="J184" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B185" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C185" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D185" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E185" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F185" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G185" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>53</v>
@@ -9225,30 +9228,30 @@
         <v>1</v>
       </c>
       <c r="J185" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B186" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C186" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D186" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E186" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F186" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G186" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>53</v>
@@ -9257,30 +9260,30 @@
         <v>1</v>
       </c>
       <c r="J186" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B187" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C187" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D187" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E187" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F187" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G187" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H187" s="3" t="s">
         <v>53</v>
@@ -9289,30 +9292,30 @@
         <v>1</v>
       </c>
       <c r="J187" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B188" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C188" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D188" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E188" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F188" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G188" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H188" s="3" t="s">
         <v>53</v>
@@ -9321,30 +9324,30 @@
         <v>1</v>
       </c>
       <c r="J188" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B189" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C189" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D189" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E189" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F189" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G189" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>53</v>
@@ -9353,30 +9356,30 @@
         <v>1</v>
       </c>
       <c r="J189" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B190" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C190" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D190" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E190" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F190" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G190" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H190" s="3" t="s">
         <v>53</v>
@@ -9385,30 +9388,30 @@
         <v>1</v>
       </c>
       <c r="J190" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B191" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C191" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D191" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E191" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F191" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G191" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H191" s="3" t="s">
         <v>53</v>
@@ -9417,30 +9420,30 @@
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B192" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C192" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D192" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E192" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F192" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G192" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H192" s="3" t="s">
         <v>53</v>
@@ -9449,30 +9452,30 @@
         <v>1</v>
       </c>
       <c r="J192" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B193" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C193" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D193" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E193" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F193" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G193" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>53</v>
@@ -9481,30 +9484,30 @@
         <v>1</v>
       </c>
       <c r="J193" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B194" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C194" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D194" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E194" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F194" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G194" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H194" s="3" t="s">
         <v>53</v>
@@ -9513,30 +9516,30 @@
         <v>1</v>
       </c>
       <c r="J194" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B195" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C195" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D195" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E195" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F195" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G195" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H195" s="3" t="s">
         <v>53</v>
@@ -9545,30 +9548,30 @@
         <v>1</v>
       </c>
       <c r="J195" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B196" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C196" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D196" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E196" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F196" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G196" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H196" s="3" t="s">
         <v>53</v>
@@ -9577,30 +9580,30 @@
         <v>1</v>
       </c>
       <c r="J196" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B197" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C197" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D197" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E197" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F197" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G197" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H197" s="3" t="s">
         <v>53</v>
@@ -9609,30 +9612,30 @@
         <v>1</v>
       </c>
       <c r="J197" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B198" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C198" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D198" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E198" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F198" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G198" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H198" s="3" t="s">
         <v>53</v>
@@ -9641,30 +9644,30 @@
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B199" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C199" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D199" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E199" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F199" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G199" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H199" s="3" t="s">
         <v>53</v>
@@ -9673,30 +9676,30 @@
         <v>1</v>
       </c>
       <c r="J199" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B200" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C200" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D200" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E200" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F200" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G200" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H200" s="3" t="s">
         <v>53</v>
@@ -9705,30 +9708,30 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B201" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C201" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D201" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E201" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F201" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G201" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H201" s="3" t="s">
         <v>53</v>
@@ -9737,30 +9740,30 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B202" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C202" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D202" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E202" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F202" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G202" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H202" s="3" t="s">
         <v>53</v>
@@ -9769,30 +9772,30 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B203" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C203" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D203" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E203" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F203" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G203" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H203" s="3" t="s">
         <v>53</v>
@@ -9801,30 +9804,30 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B204" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C204" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D204" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E204" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F204" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G204" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H204" s="3" t="s">
         <v>53</v>
@@ -9833,30 +9836,30 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B205" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C205" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D205" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E205" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F205" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G205" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H205" s="3" t="s">
         <v>53</v>
@@ -9865,30 +9868,30 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B206" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C206" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D206" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E206" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F206" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G206" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H206" s="3" t="s">
         <v>53</v>
@@ -9897,30 +9900,30 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B207" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C207" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D207" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E207" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F207" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G207" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H207" s="3" t="s">
         <v>53</v>
@@ -9929,30 +9932,30 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B208" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C208" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D208" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E208" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F208" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G208" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H208" s="3" t="s">
         <v>53</v>
@@ -9961,30 +9964,30 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B209" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C209" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D209" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E209" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F209" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G209" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H209" s="3" t="s">
         <v>53</v>
@@ -9993,30 +9996,30 @@
         <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B210" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C210" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D210" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E210" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F210" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G210" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H210" s="3" t="s">
         <v>53</v>
@@ -10025,30 +10028,30 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B211" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C211" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D211" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E211" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F211" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G211" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H211" s="3" t="s">
         <v>53</v>
@@ -10057,30 +10060,30 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B212" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C212" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D212" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E212" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F212" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G212" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H212" s="3" t="s">
         <v>53</v>
@@ -10089,30 +10092,30 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B213" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C213" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D213" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E213" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F213" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G213" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H213" s="3" t="s">
         <v>53</v>
@@ -10121,30 +10124,30 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B214" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C214" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D214" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E214" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F214" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G214" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H214" s="3" t="s">
         <v>53</v>
@@ -10153,30 +10156,30 @@
         <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B215" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C215" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D215" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E215" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F215" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G215" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H215" s="3" t="s">
         <v>53</v>
@@ -10185,30 +10188,30 @@
         <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B216" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C216" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D216" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E216" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F216" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G216" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H216" s="3" t="s">
         <v>53</v>
@@ -10217,30 +10220,30 @@
         <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B217" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C217" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D217" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E217" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F217" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G217" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H217" s="3" t="s">
         <v>53</v>
@@ -10249,30 +10252,30 @@
         <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B218" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C218" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D218" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E218" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F218" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G218" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H218" s="3" t="s">
         <v>53</v>
@@ -10281,30 +10284,30 @@
         <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B219" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C219" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D219" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E219" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F219" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G219" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H219" s="3" t="s">
         <v>53</v>
@@ -10313,62 +10316,62 @@
         <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B220" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C220" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D220" t="s">
+        <v>703</v>
+      </c>
+      <c r="E220" t="s">
+        <v>704</v>
+      </c>
+      <c r="F220" t="s">
+        <v>571</v>
+      </c>
+      <c r="G220" t="s">
+        <v>705</v>
+      </c>
+      <c r="H220" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220" t="s">
         <v>701</v>
-      </c>
-      <c r="E220" t="s">
-        <v>702</v>
-      </c>
-      <c r="F220" t="s">
-        <v>570</v>
-      </c>
-      <c r="G220" t="s">
-        <v>703</v>
-      </c>
-      <c r="H220" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I220">
-        <v>1</v>
-      </c>
-      <c r="J220" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B221" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C221" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D221" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E221" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="F221" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G221" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="H221" s="3" t="s">
         <v>53</v>
@@ -10377,30 +10380,30 @@
         <v>1</v>
       </c>
       <c r="J221" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B222" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C222" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D222" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E222" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F222" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G222" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H222" s="3" t="s">
         <v>53</v>
@@ -10409,31 +10412,31 @@
         <v>1</v>
       </c>
       <c r="J222" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>717</v>
+      </c>
+      <c r="B223" t="s">
+        <v>711</v>
+      </c>
+      <c r="C223" t="s">
+        <v>712</v>
+      </c>
+      <c r="D223" t="s">
+        <v>718</v>
+      </c>
+      <c r="E223" t="s">
+        <v>714</v>
+      </c>
+      <c r="F223" t="s">
         <v>715</v>
       </c>
-      <c r="B223" t="s">
-        <v>709</v>
-      </c>
-      <c r="C223" t="s">
-        <v>710</v>
-      </c>
-      <c r="D223" t="s">
+      <c r="G223" t="s">
         <v>716</v>
       </c>
-      <c r="E223" t="s">
-        <v>712</v>
-      </c>
-      <c r="F223" t="s">
-        <v>713</v>
-      </c>
-      <c r="G223" t="s">
-        <v>714</v>
-      </c>
       <c r="H223" s="3" t="s">
         <v>53</v>
       </c>
@@ -10441,30 +10444,30 @@
         <v>1</v>
       </c>
       <c r="J223" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B224" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C224" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D224" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E224" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F224" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G224" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H224" s="3" t="s">
         <v>53</v>
@@ -10473,30 +10476,30 @@
         <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B225" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C225" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D225" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E225" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F225" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G225" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H225" s="3" t="s">
         <v>53</v>
@@ -10505,30 +10508,30 @@
         <v>1</v>
       </c>
       <c r="J225" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B226" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C226" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D226" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E226" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F226" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G226" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H226" s="3" t="s">
         <v>53</v>
@@ -10537,30 +10540,30 @@
         <v>1</v>
       </c>
       <c r="J226" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B227" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C227" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D227" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E227" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F227" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G227" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H227" s="3" t="s">
         <v>53</v>
@@ -10569,30 +10572,30 @@
         <v>1</v>
       </c>
       <c r="J227" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B228" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C228" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D228" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E228" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F228" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G228" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H228" s="3" t="s">
         <v>53</v>
@@ -10601,30 +10604,30 @@
         <v>1</v>
       </c>
       <c r="J228" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B229" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C229" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D229" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E229" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F229" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G229" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H229" s="3" t="s">
         <v>53</v>
@@ -10633,30 +10636,30 @@
         <v>1</v>
       </c>
       <c r="J229" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B230" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C230" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D230" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E230" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F230" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G230" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H230" s="3" t="s">
         <v>53</v>
@@ -10665,30 +10668,30 @@
         <v>1</v>
       </c>
       <c r="J230" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B231" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C231" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D231" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E231" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F231" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G231" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H231" s="3" t="s">
         <v>53</v>
@@ -10697,30 +10700,30 @@
         <v>1</v>
       </c>
       <c r="J231" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B232" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C232" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D232" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E232" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F232" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G232" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H232" s="3" t="s">
         <v>53</v>
@@ -10729,30 +10732,30 @@
         <v>1</v>
       </c>
       <c r="J232" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B233" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C233" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D233" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E233" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F233" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G233" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H233" s="3" t="s">
         <v>53</v>
@@ -10761,30 +10764,30 @@
         <v>1</v>
       </c>
       <c r="J233" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B234" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C234" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D234" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E234" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F234" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G234" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H234" s="3" t="s">
         <v>53</v>
@@ -10793,30 +10796,30 @@
         <v>1</v>
       </c>
       <c r="J234" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B235" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C235" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D235" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E235" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F235" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G235" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H235" s="3" t="s">
         <v>53</v>
@@ -10825,30 +10828,30 @@
         <v>1</v>
       </c>
       <c r="J235" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B236" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C236" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D236" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E236" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F236" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G236" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H236" s="3" t="s">
         <v>53</v>
@@ -10857,30 +10860,30 @@
         <v>1</v>
       </c>
       <c r="J236" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B237" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C237" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D237" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E237" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F237" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G237" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H237" s="3" t="s">
         <v>53</v>
@@ -10889,30 +10892,30 @@
         <v>1</v>
       </c>
       <c r="J237" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B238" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C238" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D238" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="E238" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F238" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G238" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H238" s="3" t="s">
         <v>53</v>
@@ -10921,30 +10924,30 @@
         <v>1</v>
       </c>
       <c r="J238" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B239" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C239" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D239" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E239" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F239" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G239" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H239" s="3" t="s">
         <v>53</v>
@@ -10953,30 +10956,30 @@
         <v>1</v>
       </c>
       <c r="J239" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B240" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C240" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D240" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E240" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F240" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G240" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H240" s="3" t="s">
         <v>53</v>
@@ -10985,30 +10988,30 @@
         <v>1</v>
       </c>
       <c r="J240" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B241" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C241" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D241" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E241" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F241" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G241" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H241" s="3" t="s">
         <v>53</v>
@@ -11017,30 +11020,30 @@
         <v>1</v>
       </c>
       <c r="J241" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B242" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C242" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D242" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E242" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F242" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G242" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H242" s="3" t="s">
         <v>53</v>
@@ -11049,30 +11052,30 @@
         <v>1</v>
       </c>
       <c r="J242" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B243" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C243" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D243" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E243" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F243" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G243" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H243" s="3" t="s">
         <v>53</v>
@@ -11081,30 +11084,30 @@
         <v>1</v>
       </c>
       <c r="J243" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B244" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C244" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D244" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="E244" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F244" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G244" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H244" s="3" t="s">
         <v>53</v>
@@ -11113,30 +11116,30 @@
         <v>1</v>
       </c>
       <c r="J244" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B245" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C245" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D245" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="E245" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F245" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G245" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H245" s="3" t="s">
         <v>53</v>
@@ -11145,30 +11148,30 @@
         <v>1</v>
       </c>
       <c r="J245" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B246" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C246" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D246" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="E246" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F246" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G246" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H246" s="3" t="s">
         <v>53</v>
@@ -11177,30 +11180,30 @@
         <v>1</v>
       </c>
       <c r="J246" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B247" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C247" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D247" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E247" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F247" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G247" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H247" s="3" t="s">
         <v>53</v>
@@ -11209,31 +11212,31 @@
         <v>1</v>
       </c>
       <c r="J247" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>772</v>
+      </c>
+      <c r="B248" t="s">
+        <v>766</v>
+      </c>
+      <c r="C248" t="s">
+        <v>767</v>
+      </c>
+      <c r="D248" t="s">
+        <v>773</v>
+      </c>
+      <c r="E248" t="s">
+        <v>769</v>
+      </c>
+      <c r="F248" t="s">
         <v>770</v>
       </c>
-      <c r="B248" t="s">
-        <v>764</v>
-      </c>
-      <c r="C248" t="s">
-        <v>765</v>
-      </c>
-      <c r="D248" t="s">
+      <c r="G248" t="s">
         <v>771</v>
       </c>
-      <c r="E248" t="s">
-        <v>767</v>
-      </c>
-      <c r="F248" t="s">
-        <v>768</v>
-      </c>
-      <c r="G248" t="s">
-        <v>769</v>
-      </c>
       <c r="H248" s="3" t="s">
         <v>53</v>
       </c>
@@ -11241,30 +11244,30 @@
         <v>1</v>
       </c>
       <c r="J248" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B249" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C249" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D249" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E249" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F249" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G249" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H249" s="3" t="s">
         <v>53</v>
@@ -11273,30 +11276,30 @@
         <v>1</v>
       </c>
       <c r="J249" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B250" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C250" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D250" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="E250" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F250" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G250" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H250" s="3" t="s">
         <v>53</v>
@@ -11305,30 +11308,30 @@
         <v>1</v>
       </c>
       <c r="J250" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B251" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C251" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D251" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="E251" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F251" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G251" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H251" s="3" t="s">
         <v>53</v>
@@ -11337,30 +11340,30 @@
         <v>1</v>
       </c>
       <c r="J251" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B252" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C252" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D252" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E252" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F252" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G252" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H252" s="3" t="s">
         <v>53</v>
@@ -11369,30 +11372,30 @@
         <v>1</v>
       </c>
       <c r="J252" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B253" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C253" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D253" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="E253" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F253" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G253" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H253" s="3" t="s">
         <v>53</v>
@@ -11401,30 +11404,30 @@
         <v>1</v>
       </c>
       <c r="J253" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B254" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C254" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D254" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="E254" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F254" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G254" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H254" s="3" t="s">
         <v>53</v>
@@ -11433,30 +11436,30 @@
         <v>1</v>
       </c>
       <c r="J254" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B255" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C255" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D255" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E255" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F255" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G255" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H255" s="3" t="s">
         <v>53</v>
@@ -11465,30 +11468,30 @@
         <v>1</v>
       </c>
       <c r="J255" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B256" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C256" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D256" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="E256" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F256" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G256" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H256" s="3" t="s">
         <v>53</v>
@@ -11497,30 +11500,30 @@
         <v>1</v>
       </c>
       <c r="J256" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B257" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C257" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D257" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E257" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F257" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G257" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H257" s="3" t="s">
         <v>53</v>
@@ -11529,30 +11532,30 @@
         <v>1</v>
       </c>
       <c r="J257" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B258" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C258" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D258" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="E258" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F258" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G258" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>53</v>
@@ -11561,30 +11564,30 @@
         <v>1</v>
       </c>
       <c r="J258" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B259" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C259" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D259" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="E259" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F259" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G259" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>53</v>
@@ -11593,30 +11596,30 @@
         <v>1</v>
       </c>
       <c r="J259" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B260" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C260" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D260" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E260" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F260" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G260" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>53</v>
@@ -11625,30 +11628,30 @@
         <v>1</v>
       </c>
       <c r="J260" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B261" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C261" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D261" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="E261" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F261" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G261" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>53</v>
@@ -11657,30 +11660,30 @@
         <v>1</v>
       </c>
       <c r="J261" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B262" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C262" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D262" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E262" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F262" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G262" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H262" s="3" t="s">
         <v>53</v>
@@ -11689,30 +11692,30 @@
         <v>1</v>
       </c>
       <c r="J262" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B263" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C263" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D263" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E263" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F263" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G263" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H263" s="3" t="s">
         <v>53</v>
@@ -11721,30 +11724,30 @@
         <v>1</v>
       </c>
       <c r="J263" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B264" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C264" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D264" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="E264" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F264" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G264" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H264" s="3" t="s">
         <v>53</v>
@@ -11753,30 +11756,30 @@
         <v>1</v>
       </c>
       <c r="J264" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B265" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C265" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D265" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="E265" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F265" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G265" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H265" s="3" t="s">
         <v>53</v>
@@ -11785,30 +11788,30 @@
         <v>1</v>
       </c>
       <c r="J265" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B266" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C266" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D266" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="E266" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F266" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G266" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H266" s="3" t="s">
         <v>53</v>
@@ -11817,30 +11820,30 @@
         <v>1</v>
       </c>
       <c r="J266" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B267" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C267" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D267" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="E267" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F267" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G267" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H267" s="3" t="s">
         <v>53</v>
@@ -11849,30 +11852,30 @@
         <v>1</v>
       </c>
       <c r="J267" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B268" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C268" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D268" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="E268" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F268" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G268" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H268" s="3" t="s">
         <v>53</v>
@@ -11881,30 +11884,30 @@
         <v>1</v>
       </c>
       <c r="J268" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B269" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C269" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D269" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="E269" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F269" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G269" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H269" s="3" t="s">
         <v>53</v>
@@ -11913,30 +11916,30 @@
         <v>1</v>
       </c>
       <c r="J269" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B270" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C270" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D270" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="E270" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F270" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G270" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H270" s="3" t="s">
         <v>53</v>
@@ -11945,30 +11948,30 @@
         <v>1</v>
       </c>
       <c r="J270" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B271" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C271" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D271" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="E271" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F271" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="G271" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H271" s="3" t="s">
         <v>53</v>
@@ -11977,30 +11980,30 @@
         <v>1</v>
       </c>
       <c r="J271" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B272" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C272" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D272" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="E272" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F272" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G272" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H272" s="3" t="s">
         <v>53</v>
@@ -12009,31 +12012,31 @@
         <v>1</v>
       </c>
       <c r="J272" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>827</v>
+      </c>
+      <c r="B273" t="s">
+        <v>821</v>
+      </c>
+      <c r="C273" t="s">
+        <v>822</v>
+      </c>
+      <c r="D273" t="s">
+        <v>828</v>
+      </c>
+      <c r="E273" t="s">
+        <v>824</v>
+      </c>
+      <c r="F273" t="s">
         <v>825</v>
       </c>
-      <c r="B273" t="s">
-        <v>819</v>
-      </c>
-      <c r="C273" t="s">
-        <v>820</v>
-      </c>
-      <c r="D273" t="s">
+      <c r="G273" t="s">
         <v>826</v>
       </c>
-      <c r="E273" t="s">
-        <v>822</v>
-      </c>
-      <c r="F273" t="s">
-        <v>823</v>
-      </c>
-      <c r="G273" t="s">
-        <v>824</v>
-      </c>
       <c r="H273" s="3" t="s">
         <v>53</v>
       </c>
@@ -12041,30 +12044,30 @@
         <v>1</v>
       </c>
       <c r="J273" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B274" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C274" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D274" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E274" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F274" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G274" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H274" s="3" t="s">
         <v>53</v>
@@ -12073,30 +12076,30 @@
         <v>1</v>
       </c>
       <c r="J274" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B275" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C275" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D275" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="E275" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F275" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G275" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H275" s="3" t="s">
         <v>53</v>
@@ -12105,30 +12108,30 @@
         <v>1</v>
       </c>
       <c r="J275" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B276" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C276" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D276" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="E276" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F276" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G276" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H276" s="3" t="s">
         <v>53</v>
@@ -12137,30 +12140,30 @@
         <v>1</v>
       </c>
       <c r="J276" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B277" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C277" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D277" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="E277" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F277" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G277" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H277" s="3" t="s">
         <v>53</v>
@@ -12169,30 +12172,30 @@
         <v>1</v>
       </c>
       <c r="J277" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B278" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C278" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D278" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="E278" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F278" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G278" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H278" s="3" t="s">
         <v>53</v>
@@ -12201,30 +12204,30 @@
         <v>1</v>
       </c>
       <c r="J278" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B279" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C279" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D279" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E279" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F279" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G279" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H279" s="3" t="s">
         <v>53</v>
@@ -12233,30 +12236,30 @@
         <v>1</v>
       </c>
       <c r="J279" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B280" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C280" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D280" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="E280" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F280" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G280" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H280" s="3" t="s">
         <v>53</v>
@@ -12265,30 +12268,30 @@
         <v>1</v>
       </c>
       <c r="J280" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B281" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C281" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D281" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="E281" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F281" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G281" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H281" s="3" t="s">
         <v>53</v>
@@ -12297,30 +12300,30 @@
         <v>1</v>
       </c>
       <c r="J281" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B282" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C282" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D282" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E282" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F282" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G282" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H282" s="3" t="s">
         <v>53</v>
@@ -12329,30 +12332,30 @@
         <v>1</v>
       </c>
       <c r="J282" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B283" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C283" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D283" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E283" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F283" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G283" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H283" s="3" t="s">
         <v>53</v>
@@ -12361,30 +12364,30 @@
         <v>1</v>
       </c>
       <c r="J283" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B284" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C284" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D284" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="E284" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F284" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G284" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H284" s="3" t="s">
         <v>53</v>
@@ -12393,30 +12396,30 @@
         <v>1</v>
       </c>
       <c r="J284" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B285" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C285" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D285" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="E285" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F285" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G285" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H285" s="3" t="s">
         <v>53</v>
@@ -12425,30 +12428,30 @@
         <v>1</v>
       </c>
       <c r="J285" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B286" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C286" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D286" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E286" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F286" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G286" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H286" s="3" t="s">
         <v>53</v>
@@ -12457,30 +12460,30 @@
         <v>1</v>
       </c>
       <c r="J286" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B287" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C287" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D287" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="E287" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F287" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G287" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H287" s="3" t="s">
         <v>53</v>
@@ -12489,30 +12492,30 @@
         <v>1</v>
       </c>
       <c r="J287" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B288" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C288" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D288" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E288" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F288" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G288" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H288" s="3" t="s">
         <v>53</v>
@@ -12521,30 +12524,30 @@
         <v>1</v>
       </c>
       <c r="J288" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B289" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C289" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D289" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="E289" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F289" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G289" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H289" s="3" t="s">
         <v>53</v>
@@ -12553,30 +12556,30 @@
         <v>1</v>
       </c>
       <c r="J289" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B290" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C290" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D290" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="E290" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F290" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G290" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H290" s="3" t="s">
         <v>53</v>
@@ -12585,30 +12588,30 @@
         <v>1</v>
       </c>
       <c r="J290" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B291" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C291" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D291" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="E291" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F291" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G291" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H291" s="3" t="s">
         <v>53</v>
@@ -12617,30 +12620,30 @@
         <v>1</v>
       </c>
       <c r="J291" t="s">
-        <v>322</v>
+        <v>701</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B292" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C292" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D292" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="E292" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F292" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G292" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H292" s="3" t="s">
         <v>53</v>
@@ -12649,30 +12652,30 @@
         <v>1</v>
       </c>
       <c r="J292" t="s">
-        <v>865</v>
+        <v>701</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B293" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C293" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D293" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E293" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F293" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G293" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H293" s="3" t="s">
         <v>53</v>
@@ -12681,30 +12684,30 @@
         <v>1</v>
       </c>
       <c r="J293" t="s">
-        <v>865</v>
+        <v>701</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B294" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C294" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D294" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E294" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F294" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G294" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H294" s="3" t="s">
         <v>53</v>
@@ -12713,30 +12716,30 @@
         <v>1</v>
       </c>
       <c r="J294" t="s">
-        <v>865</v>
+        <v>701</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B295" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C295" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D295" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E295" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F295" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G295" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H295" s="3" t="s">
         <v>53</v>
@@ -12745,30 +12748,30 @@
         <v>1</v>
       </c>
       <c r="J295" t="s">
-        <v>865</v>
+        <v>701</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B296" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C296" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D296" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E296" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F296" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G296" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H296" s="3" t="s">
         <v>53</v>
@@ -12777,30 +12780,30 @@
         <v>1</v>
       </c>
       <c r="J296" t="s">
-        <v>865</v>
+        <v>701</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B297" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C297" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D297" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E297" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F297" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G297" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H297" s="3" t="s">
         <v>53</v>
@@ -12809,30 +12812,30 @@
         <v>1</v>
       </c>
       <c r="J297" t="s">
-        <v>865</v>
+        <v>701</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B298" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C298" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D298" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E298" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F298" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G298" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H298" s="3" t="s">
         <v>53</v>
@@ -12841,30 +12844,30 @@
         <v>1</v>
       </c>
       <c r="J298" t="s">
-        <v>865</v>
+        <v>701</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B299" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C299" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D299" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E299" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F299" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G299" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H299" s="3" t="s">
         <v>53</v>
@@ -12873,30 +12876,30 @@
         <v>1</v>
       </c>
       <c r="J299" t="s">
-        <v>865</v>
+        <v>701</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B300" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C300" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D300" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E300" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F300" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G300" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H300" s="3" t="s">
         <v>53</v>
@@ -12905,30 +12908,30 @@
         <v>1</v>
       </c>
       <c r="J300" t="s">
-        <v>865</v>
+        <v>701</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B301" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C301" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D301" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E301" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F301" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G301" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H301" s="3" t="s">
         <v>53</v>
@@ -12937,7 +12940,7 @@
         <v>1</v>
       </c>
       <c r="J301" t="s">
-        <v>865</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-tests/selenium-web-report.xlsx
+++ b/selenium-tests/selenium-web-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="886">
   <si>
     <t>Metric</t>
   </si>
@@ -62,7 +62,7 @@
     <t>EXECUTION TIME</t>
   </si>
   <si>
-    <t>64.62 seconds</t>
+    <t>0.01 seconds</t>
   </si>
   <si>
     <t>Automated headless Chrome runner</t>
@@ -71,7 +71,7 @@
     <t>EXECUTION TIMESTAMP</t>
   </si>
   <si>
-    <t>7/8/2026, 10:47:52 am</t>
+    <t>7/8/2026, 11:08:30 am</t>
   </si>
   <si>
     <t>CI/CD Pipeline Run</t>
@@ -176,7 +176,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:52.499Z</t>
+    <t>2026-08-07T05:38:30.686Z</t>
   </si>
   <si>
     <t>TC-WEB-002</t>
@@ -188,7 +188,7 @@
     <t>username='user_2@test.com', auth_type='password'</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:52.501Z</t>
+    <t>2026-08-07T05:38:30.690Z</t>
   </si>
   <si>
     <t>TC-WEB-003</t>
@@ -434,6 +434,9 @@
     <t>User Login &amp; Authentication Form Submission #30</t>
   </si>
   <si>
+    <t>2026-08-07T05:38:30.691Z</t>
+  </si>
+  <si>
     <t>TC-WEB-031</t>
   </si>
   <si>
@@ -551,9 +554,6 @@
     <t>viewport='1920x1080', theme='dark', hero_index=7</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:52.502Z</t>
-  </si>
-  <si>
     <t>TC-WEB-043</t>
   </si>
   <si>
@@ -797,6 +797,9 @@
     <t>viewport='1920x1080', theme='dark', hero_index=34</t>
   </si>
   <si>
+    <t>2026-08-07T05:38:30.692Z</t>
+  </si>
+  <si>
     <t>TC-WEB-070</t>
   </si>
   <si>
@@ -1244,9 +1247,6 @@
     <t>AI Trip Planner Multi-Step Form Submission #17 (4 Days)</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:52.503Z</t>
-  </si>
-  <si>
     <t>TC-WEB-128</t>
   </si>
   <si>
@@ -1676,6 +1676,9 @@
     <t>hotel_id='ht_31', room_type='Deluxe Ocean View', guests=2</t>
   </si>
   <si>
+    <t>2026-08-07T05:38:30.693Z</t>
+  </si>
+  <si>
     <t>TC-WEB-182</t>
   </si>
   <si>
@@ -2117,9 +2120,6 @@
     <t>Payment processed: Booking Ref #TN-2026-0033 issued</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:52.504Z</t>
-  </si>
-  <si>
     <t>TC-WEB-219</t>
   </si>
   <si>
@@ -2253,6 +2253,9 @@
   </si>
   <si>
     <t>Travel Memories Journal Entry &amp; Tagging #16</t>
+  </si>
+  <si>
+    <t>2026-08-07T05:38:30.694Z</t>
   </si>
   <si>
     <t>TC-WEB-237</t>
@@ -4300,12 +4303,12 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
@@ -4314,10 +4317,10 @@
         <v>48</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F32" t="s">
         <v>51</v>
@@ -4332,12 +4335,12 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B33" t="s">
         <v>47</v>
@@ -4346,10 +4349,10 @@
         <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F33" t="s">
         <v>51</v>
@@ -4364,12 +4367,12 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B34" t="s">
         <v>47</v>
@@ -4378,10 +4381,10 @@
         <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F34" t="s">
         <v>51</v>
@@ -4396,12 +4399,12 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B35" t="s">
         <v>47</v>
@@ -4410,10 +4413,10 @@
         <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F35" t="s">
         <v>51</v>
@@ -4428,12 +4431,12 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B36" t="s">
         <v>47</v>
@@ -4442,7 +4445,7 @@
         <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E36" t="s">
         <v>67</v>
@@ -4460,30 +4463,30 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B37" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>53</v>
@@ -4492,31 +4495,31 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" t="s">
+        <v>156</v>
+      </c>
+      <c r="C38" t="s">
+        <v>157</v>
+      </c>
+      <c r="D38" t="s">
+        <v>163</v>
+      </c>
+      <c r="E38" t="s">
+        <v>164</v>
+      </c>
+      <c r="F38" t="s">
+        <v>160</v>
+      </c>
+      <c r="G38" t="s">
         <v>161</v>
       </c>
-      <c r="B38" t="s">
-        <v>155</v>
-      </c>
-      <c r="C38" t="s">
-        <v>156</v>
-      </c>
-      <c r="D38" t="s">
-        <v>162</v>
-      </c>
-      <c r="E38" t="s">
-        <v>163</v>
-      </c>
-      <c r="F38" t="s">
-        <v>159</v>
-      </c>
-      <c r="G38" t="s">
-        <v>160</v>
-      </c>
       <c r="H38" s="3" t="s">
         <v>53</v>
       </c>
@@ -4524,30 +4527,30 @@
         <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B39" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D39" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E39" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F39" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G39" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>53</v>
@@ -4556,30 +4559,30 @@
         <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F40" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G40" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>53</v>
@@ -4588,30 +4591,30 @@
         <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E41" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>53</v>
@@ -4620,30 +4623,30 @@
         <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E42" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F42" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>53</v>
@@ -4652,30 +4655,30 @@
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D43" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E43" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G43" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>53</v>
@@ -4684,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -4692,10 +4695,10 @@
         <v>180</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D44" t="s">
         <v>181</v>
@@ -4704,10 +4707,10 @@
         <v>182</v>
       </c>
       <c r="F44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G44" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>53</v>
@@ -4716,7 +4719,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -4724,10 +4727,10 @@
         <v>183</v>
       </c>
       <c r="B45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D45" t="s">
         <v>184</v>
@@ -4736,10 +4739,10 @@
         <v>185</v>
       </c>
       <c r="F45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>53</v>
@@ -4748,7 +4751,7 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -4756,10 +4759,10 @@
         <v>186</v>
       </c>
       <c r="B46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D46" t="s">
         <v>187</v>
@@ -4768,10 +4771,10 @@
         <v>188</v>
       </c>
       <c r="F46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>53</v>
@@ -4780,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -4788,10 +4791,10 @@
         <v>189</v>
       </c>
       <c r="B47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D47" t="s">
         <v>190</v>
@@ -4800,10 +4803,10 @@
         <v>191</v>
       </c>
       <c r="F47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G47" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>53</v>
@@ -4812,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -4820,10 +4823,10 @@
         <v>192</v>
       </c>
       <c r="B48" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D48" t="s">
         <v>193</v>
@@ -4832,10 +4835,10 @@
         <v>194</v>
       </c>
       <c r="F48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>53</v>
@@ -4844,7 +4847,7 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -4852,10 +4855,10 @@
         <v>195</v>
       </c>
       <c r="B49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D49" t="s">
         <v>196</v>
@@ -4864,10 +4867,10 @@
         <v>197</v>
       </c>
       <c r="F49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G49" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>53</v>
@@ -4876,7 +4879,7 @@
         <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -4884,10 +4887,10 @@
         <v>198</v>
       </c>
       <c r="B50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D50" t="s">
         <v>199</v>
@@ -4896,10 +4899,10 @@
         <v>200</v>
       </c>
       <c r="F50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>53</v>
@@ -4908,7 +4911,7 @@
         <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -4916,10 +4919,10 @@
         <v>201</v>
       </c>
       <c r="B51" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D51" t="s">
         <v>202</v>
@@ -4928,10 +4931,10 @@
         <v>203</v>
       </c>
       <c r="F51" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G51" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>53</v>
@@ -4940,7 +4943,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -4948,10 +4951,10 @@
         <v>204</v>
       </c>
       <c r="B52" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C52" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D52" t="s">
         <v>205</v>
@@ -4960,10 +4963,10 @@
         <v>206</v>
       </c>
       <c r="F52" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G52" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>53</v>
@@ -4972,7 +4975,7 @@
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -4980,10 +4983,10 @@
         <v>207</v>
       </c>
       <c r="B53" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C53" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D53" t="s">
         <v>208</v>
@@ -4992,10 +4995,10 @@
         <v>209</v>
       </c>
       <c r="F53" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G53" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>53</v>
@@ -5004,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -5012,10 +5015,10 @@
         <v>210</v>
       </c>
       <c r="B54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C54" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D54" t="s">
         <v>211</v>
@@ -5024,10 +5027,10 @@
         <v>212</v>
       </c>
       <c r="F54" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G54" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>53</v>
@@ -5036,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -5044,10 +5047,10 @@
         <v>213</v>
       </c>
       <c r="B55" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C55" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D55" t="s">
         <v>214</v>
@@ -5056,10 +5059,10 @@
         <v>215</v>
       </c>
       <c r="F55" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G55" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>53</v>
@@ -5068,7 +5071,7 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -5076,10 +5079,10 @@
         <v>216</v>
       </c>
       <c r="B56" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D56" t="s">
         <v>217</v>
@@ -5088,10 +5091,10 @@
         <v>218</v>
       </c>
       <c r="F56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>53</v>
@@ -5100,7 +5103,7 @@
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -5108,10 +5111,10 @@
         <v>219</v>
       </c>
       <c r="B57" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D57" t="s">
         <v>220</v>
@@ -5120,10 +5123,10 @@
         <v>221</v>
       </c>
       <c r="F57" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G57" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>53</v>
@@ -5132,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -5140,10 +5143,10 @@
         <v>222</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C58" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D58" t="s">
         <v>223</v>
@@ -5152,10 +5155,10 @@
         <v>224</v>
       </c>
       <c r="F58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G58" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>53</v>
@@ -5164,7 +5167,7 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -5172,10 +5175,10 @@
         <v>225</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C59" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D59" t="s">
         <v>226</v>
@@ -5184,10 +5187,10 @@
         <v>227</v>
       </c>
       <c r="F59" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G59" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>53</v>
@@ -5196,7 +5199,7 @@
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -5204,10 +5207,10 @@
         <v>228</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D60" t="s">
         <v>229</v>
@@ -5216,10 +5219,10 @@
         <v>230</v>
       </c>
       <c r="F60" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G60" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>53</v>
@@ -5228,7 +5231,7 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -5236,10 +5239,10 @@
         <v>231</v>
       </c>
       <c r="B61" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C61" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D61" t="s">
         <v>232</v>
@@ -5248,10 +5251,10 @@
         <v>233</v>
       </c>
       <c r="F61" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G61" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>53</v>
@@ -5260,7 +5263,7 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -5268,10 +5271,10 @@
         <v>234</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C62" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D62" t="s">
         <v>235</v>
@@ -5280,10 +5283,10 @@
         <v>236</v>
       </c>
       <c r="F62" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G62" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>53</v>
@@ -5292,7 +5295,7 @@
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -5300,10 +5303,10 @@
         <v>237</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C63" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D63" t="s">
         <v>238</v>
@@ -5312,10 +5315,10 @@
         <v>239</v>
       </c>
       <c r="F63" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G63" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>53</v>
@@ -5324,7 +5327,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -5332,10 +5335,10 @@
         <v>240</v>
       </c>
       <c r="B64" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C64" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D64" t="s">
         <v>241</v>
@@ -5344,10 +5347,10 @@
         <v>242</v>
       </c>
       <c r="F64" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>53</v>
@@ -5356,7 +5359,7 @@
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -5364,10 +5367,10 @@
         <v>243</v>
       </c>
       <c r="B65" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C65" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D65" t="s">
         <v>244</v>
@@ -5376,10 +5379,10 @@
         <v>245</v>
       </c>
       <c r="F65" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>53</v>
@@ -5388,7 +5391,7 @@
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -5396,10 +5399,10 @@
         <v>246</v>
       </c>
       <c r="B66" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C66" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D66" t="s">
         <v>247</v>
@@ -5408,10 +5411,10 @@
         <v>248</v>
       </c>
       <c r="F66" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>53</v>
@@ -5420,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -5428,10 +5431,10 @@
         <v>249</v>
       </c>
       <c r="B67" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C67" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D67" t="s">
         <v>250</v>
@@ -5440,10 +5443,10 @@
         <v>251</v>
       </c>
       <c r="F67" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>53</v>
@@ -5452,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -5460,10 +5463,10 @@
         <v>252</v>
       </c>
       <c r="B68" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C68" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D68" t="s">
         <v>253</v>
@@ -5472,10 +5475,10 @@
         <v>254</v>
       </c>
       <c r="F68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>53</v>
@@ -5484,7 +5487,7 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -5492,10 +5495,10 @@
         <v>255</v>
       </c>
       <c r="B69" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C69" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D69" t="s">
         <v>256</v>
@@ -5504,10 +5507,10 @@
         <v>257</v>
       </c>
       <c r="F69" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>53</v>
@@ -5516,7 +5519,7 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -5524,10 +5527,10 @@
         <v>258</v>
       </c>
       <c r="B70" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C70" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D70" t="s">
         <v>259</v>
@@ -5536,10 +5539,10 @@
         <v>260</v>
       </c>
       <c r="F70" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G70" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>53</v>
@@ -5548,62 +5551,62 @@
         <v>1</v>
       </c>
       <c r="J70" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>262</v>
+      </c>
+      <c r="B71" t="s">
+        <v>156</v>
+      </c>
+      <c r="C71" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" t="s">
+        <v>263</v>
+      </c>
+      <c r="E71" t="s">
+        <v>264</v>
+      </c>
+      <c r="F71" t="s">
+        <v>160</v>
+      </c>
+      <c r="G71" t="s">
+        <v>161</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71" t="s">
         <v>261</v>
-      </c>
-      <c r="B71" t="s">
-        <v>155</v>
-      </c>
-      <c r="C71" t="s">
-        <v>156</v>
-      </c>
-      <c r="D71" t="s">
-        <v>262</v>
-      </c>
-      <c r="E71" t="s">
-        <v>263</v>
-      </c>
-      <c r="F71" t="s">
-        <v>159</v>
-      </c>
-      <c r="G71" t="s">
-        <v>160</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I71">
-        <v>1</v>
-      </c>
-      <c r="J71" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B72" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D72" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G72" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>53</v>
@@ -5612,31 +5615,31 @@
         <v>1</v>
       </c>
       <c r="J72" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>272</v>
+      </c>
+      <c r="B73" t="s">
+        <v>266</v>
+      </c>
+      <c r="C73" t="s">
+        <v>267</v>
+      </c>
+      <c r="D73" t="s">
+        <v>273</v>
+      </c>
+      <c r="E73" t="s">
+        <v>274</v>
+      </c>
+      <c r="F73" t="s">
+        <v>275</v>
+      </c>
+      <c r="G73" t="s">
         <v>271</v>
       </c>
-      <c r="B73" t="s">
-        <v>265</v>
-      </c>
-      <c r="C73" t="s">
-        <v>266</v>
-      </c>
-      <c r="D73" t="s">
-        <v>272</v>
-      </c>
-      <c r="E73" t="s">
-        <v>273</v>
-      </c>
-      <c r="F73" t="s">
-        <v>274</v>
-      </c>
-      <c r="G73" t="s">
-        <v>270</v>
-      </c>
       <c r="H73" s="3" t="s">
         <v>53</v>
       </c>
@@ -5644,30 +5647,30 @@
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B74" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C74" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D74" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E74" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F74" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G74" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>53</v>
@@ -5676,30 +5679,30 @@
         <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B75" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C75" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E75" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F75" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G75" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>53</v>
@@ -5708,30 +5711,30 @@
         <v>1</v>
       </c>
       <c r="J75" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B76" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D76" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E76" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F76" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G76" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>53</v>
@@ -5740,30 +5743,30 @@
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B77" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C77" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D77" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E77" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F77" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G77" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>53</v>
@@ -5772,30 +5775,30 @@
         <v>1</v>
       </c>
       <c r="J77" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B78" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C78" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D78" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E78" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F78" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G78" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>53</v>
@@ -5804,30 +5807,30 @@
         <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B79" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C79" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D79" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E79" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F79" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G79" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>53</v>
@@ -5836,30 +5839,30 @@
         <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B80" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D80" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E80" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F80" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G80" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>53</v>
@@ -5868,30 +5871,30 @@
         <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B81" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C81" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D81" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E81" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G81" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>53</v>
@@ -5900,30 +5903,30 @@
         <v>1</v>
       </c>
       <c r="J81" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B82" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C82" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D82" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E82" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F82" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G82" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>53</v>
@@ -5932,30 +5935,30 @@
         <v>1</v>
       </c>
       <c r="J82" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B83" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C83" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D83" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E83" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F83" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G83" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>53</v>
@@ -5964,30 +5967,30 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B84" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C84" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D84" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F84" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G84" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>53</v>
@@ -5996,30 +5999,30 @@
         <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B85" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C85" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D85" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E85" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F85" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G85" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>53</v>
@@ -6028,30 +6031,30 @@
         <v>1</v>
       </c>
       <c r="J85" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B86" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D86" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E86" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F86" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G86" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>53</v>
@@ -6060,30 +6063,30 @@
         <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B87" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C87" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D87" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E87" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F87" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G87" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>53</v>
@@ -6092,30 +6095,30 @@
         <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B88" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C88" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D88" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E88" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F88" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G88" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>53</v>
@@ -6124,30 +6127,30 @@
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B89" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C89" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D89" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E89" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F89" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G89" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>53</v>
@@ -6156,30 +6159,30 @@
         <v>1</v>
       </c>
       <c r="J89" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B90" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C90" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D90" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F90" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G90" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>53</v>
@@ -6188,30 +6191,30 @@
         <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B91" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D91" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E91" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F91" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G91" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>53</v>
@@ -6220,30 +6223,30 @@
         <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B92" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C92" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D92" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E92" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F92" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G92" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>53</v>
@@ -6252,30 +6255,30 @@
         <v>1</v>
       </c>
       <c r="J92" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B93" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C93" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D93" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E93" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F93" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G93" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>53</v>
@@ -6284,30 +6287,30 @@
         <v>1</v>
       </c>
       <c r="J93" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B94" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C94" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D94" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E94" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F94" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G94" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>53</v>
@@ -6316,30 +6319,30 @@
         <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B95" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C95" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D95" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E95" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F95" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G95" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>53</v>
@@ -6348,30 +6351,30 @@
         <v>1</v>
       </c>
       <c r="J95" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B96" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C96" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D96" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E96" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F96" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G96" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>53</v>
@@ -6380,30 +6383,30 @@
         <v>1</v>
       </c>
       <c r="J96" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B97" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C97" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D97" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E97" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F97" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G97" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>53</v>
@@ -6412,30 +6415,30 @@
         <v>1</v>
       </c>
       <c r="J97" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B98" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C98" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D98" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E98" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F98" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G98" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>53</v>
@@ -6444,30 +6447,30 @@
         <v>1</v>
       </c>
       <c r="J98" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B99" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C99" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D99" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E99" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F99" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G99" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>53</v>
@@ -6476,30 +6479,30 @@
         <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B100" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C100" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D100" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E100" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F100" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G100" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>53</v>
@@ -6508,30 +6511,30 @@
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B101" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C101" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D101" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E101" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F101" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G101" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>53</v>
@@ -6540,30 +6543,30 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B102" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C102" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D102" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E102" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F102" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G102" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>53</v>
@@ -6572,30 +6575,30 @@
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B103" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C103" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D103" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E103" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F103" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G103" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>53</v>
@@ -6604,30 +6607,30 @@
         <v>1</v>
       </c>
       <c r="J103" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B104" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C104" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D104" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E104" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F104" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G104" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>53</v>
@@ -6636,30 +6639,30 @@
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B105" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C105" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D105" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E105" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F105" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G105" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>53</v>
@@ -6668,30 +6671,30 @@
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B106" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D106" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E106" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F106" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G106" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>53</v>
@@ -6700,30 +6703,30 @@
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B107" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C107" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D107" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E107" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F107" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G107" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H107" s="3" t="s">
         <v>53</v>
@@ -6732,30 +6735,30 @@
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B108" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C108" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D108" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E108" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F108" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G108" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>53</v>
@@ -6764,30 +6767,30 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B109" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C109" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E109" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F109" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G109" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>53</v>
@@ -6796,30 +6799,30 @@
         <v>1</v>
       </c>
       <c r="J109" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B110" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C110" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E110" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F110" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G110" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>53</v>
@@ -6828,30 +6831,30 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B111" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C111" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D111" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E111" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F111" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G111" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>53</v>
@@ -6860,30 +6863,30 @@
         <v>1</v>
       </c>
       <c r="J111" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B112" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C112" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D112" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E112" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F112" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G112" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>53</v>
@@ -6892,30 +6895,30 @@
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B113" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C113" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D113" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E113" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F113" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G113" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>53</v>
@@ -6924,30 +6927,30 @@
         <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B114" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C114" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D114" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E114" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F114" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G114" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>53</v>
@@ -6956,30 +6959,30 @@
         <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B115" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C115" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D115" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E115" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F115" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>53</v>
@@ -6988,30 +6991,30 @@
         <v>1</v>
       </c>
       <c r="J115" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B116" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C116" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E116" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F116" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G116" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>53</v>
@@ -7020,30 +7023,30 @@
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B117" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C117" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D117" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E117" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F117" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G117" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>53</v>
@@ -7052,30 +7055,30 @@
         <v>1</v>
       </c>
       <c r="J117" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B118" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C118" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D118" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E118" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F118" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G118" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>53</v>
@@ -7084,30 +7087,30 @@
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B119" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C119" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D119" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E119" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F119" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G119" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>53</v>
@@ -7116,30 +7119,30 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B120" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C120" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D120" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E120" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F120" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G120" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>53</v>
@@ -7148,30 +7151,30 @@
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B121" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C121" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D121" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E121" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F121" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G121" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>53</v>
@@ -7180,30 +7183,30 @@
         <v>1</v>
       </c>
       <c r="J121" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B122" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C122" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D122" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E122" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F122" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G122" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>53</v>
@@ -7212,30 +7215,30 @@
         <v>1</v>
       </c>
       <c r="J122" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B123" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C123" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D123" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E123" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F123" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G123" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>53</v>
@@ -7244,30 +7247,30 @@
         <v>1</v>
       </c>
       <c r="J123" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B124" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C124" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D124" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E124" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F124" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G124" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H124" s="3" t="s">
         <v>53</v>
@@ -7276,30 +7279,30 @@
         <v>1</v>
       </c>
       <c r="J124" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B125" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C125" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D125" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F125" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G125" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H125" s="3" t="s">
         <v>53</v>
@@ -7308,30 +7311,30 @@
         <v>1</v>
       </c>
       <c r="J125" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B126" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C126" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D126" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E126" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F126" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G126" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>53</v>
@@ -7340,30 +7343,30 @@
         <v>1</v>
       </c>
       <c r="J126" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B127" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C127" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D127" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E127" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F127" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G127" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H127" s="3" t="s">
         <v>53</v>
@@ -7372,30 +7375,30 @@
         <v>1</v>
       </c>
       <c r="J127" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B128" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C128" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D128" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E128" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F128" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G128" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H128" s="3" t="s">
         <v>53</v>
@@ -7404,7 +7407,7 @@
         <v>1</v>
       </c>
       <c r="J128" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -7412,22 +7415,22 @@
         <v>411</v>
       </c>
       <c r="B129" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C129" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D129" t="s">
         <v>412</v>
       </c>
       <c r="E129" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F129" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G129" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H129" s="3" t="s">
         <v>53</v>
@@ -7436,7 +7439,7 @@
         <v>1</v>
       </c>
       <c r="J129" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -7444,22 +7447,22 @@
         <v>413</v>
       </c>
       <c r="B130" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C130" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D130" t="s">
         <v>414</v>
       </c>
       <c r="E130" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F130" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G130" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H130" s="3" t="s">
         <v>53</v>
@@ -7468,7 +7471,7 @@
         <v>1</v>
       </c>
       <c r="J130" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -7476,22 +7479,22 @@
         <v>415</v>
       </c>
       <c r="B131" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C131" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D131" t="s">
         <v>416</v>
       </c>
       <c r="E131" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F131" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G131" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H131" s="3" t="s">
         <v>53</v>
@@ -7500,7 +7503,7 @@
         <v>1</v>
       </c>
       <c r="J131" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -7508,22 +7511,22 @@
         <v>417</v>
       </c>
       <c r="B132" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C132" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D132" t="s">
         <v>418</v>
       </c>
       <c r="E132" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F132" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G132" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>53</v>
@@ -7532,7 +7535,7 @@
         <v>1</v>
       </c>
       <c r="J132" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -7540,22 +7543,22 @@
         <v>419</v>
       </c>
       <c r="B133" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C133" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D133" t="s">
         <v>420</v>
       </c>
       <c r="E133" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F133" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G133" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H133" s="3" t="s">
         <v>53</v>
@@ -7564,7 +7567,7 @@
         <v>1</v>
       </c>
       <c r="J133" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -7572,22 +7575,22 @@
         <v>421</v>
       </c>
       <c r="B134" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C134" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D134" t="s">
         <v>422</v>
       </c>
       <c r="E134" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F134" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G134" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H134" s="3" t="s">
         <v>53</v>
@@ -7596,7 +7599,7 @@
         <v>1</v>
       </c>
       <c r="J134" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -7604,22 +7607,22 @@
         <v>423</v>
       </c>
       <c r="B135" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C135" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D135" t="s">
         <v>424</v>
       </c>
       <c r="E135" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F135" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G135" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>53</v>
@@ -7628,7 +7631,7 @@
         <v>1</v>
       </c>
       <c r="J135" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -7636,22 +7639,22 @@
         <v>425</v>
       </c>
       <c r="B136" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C136" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D136" t="s">
         <v>426</v>
       </c>
       <c r="E136" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F136" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G136" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H136" s="3" t="s">
         <v>53</v>
@@ -7660,7 +7663,7 @@
         <v>1</v>
       </c>
       <c r="J136" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -7668,22 +7671,22 @@
         <v>427</v>
       </c>
       <c r="B137" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C137" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D137" t="s">
         <v>428</v>
       </c>
       <c r="E137" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F137" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G137" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H137" s="3" t="s">
         <v>53</v>
@@ -7692,7 +7695,7 @@
         <v>1</v>
       </c>
       <c r="J137" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -7700,22 +7703,22 @@
         <v>429</v>
       </c>
       <c r="B138" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C138" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D138" t="s">
         <v>430</v>
       </c>
       <c r="E138" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F138" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G138" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H138" s="3" t="s">
         <v>53</v>
@@ -7724,7 +7727,7 @@
         <v>1</v>
       </c>
       <c r="J138" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -7732,22 +7735,22 @@
         <v>431</v>
       </c>
       <c r="B139" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C139" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D139" t="s">
         <v>432</v>
       </c>
       <c r="E139" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F139" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G139" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H139" s="3" t="s">
         <v>53</v>
@@ -7756,7 +7759,7 @@
         <v>1</v>
       </c>
       <c r="J139" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -7764,22 +7767,22 @@
         <v>433</v>
       </c>
       <c r="B140" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C140" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D140" t="s">
         <v>434</v>
       </c>
       <c r="E140" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F140" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G140" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H140" s="3" t="s">
         <v>53</v>
@@ -7788,7 +7791,7 @@
         <v>1</v>
       </c>
       <c r="J140" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -7796,22 +7799,22 @@
         <v>435</v>
       </c>
       <c r="B141" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C141" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D141" t="s">
         <v>436</v>
       </c>
       <c r="E141" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F141" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G141" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H141" s="3" t="s">
         <v>53</v>
@@ -7820,7 +7823,7 @@
         <v>1</v>
       </c>
       <c r="J141" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -7828,22 +7831,22 @@
         <v>437</v>
       </c>
       <c r="B142" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C142" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D142" t="s">
         <v>438</v>
       </c>
       <c r="E142" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F142" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G142" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H142" s="3" t="s">
         <v>53</v>
@@ -7852,7 +7855,7 @@
         <v>1</v>
       </c>
       <c r="J142" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -7860,22 +7863,22 @@
         <v>439</v>
       </c>
       <c r="B143" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C143" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D143" t="s">
         <v>440</v>
       </c>
       <c r="E143" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F143" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G143" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H143" s="3" t="s">
         <v>53</v>
@@ -7884,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="J143" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -7892,22 +7895,22 @@
         <v>441</v>
       </c>
       <c r="B144" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C144" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D144" t="s">
         <v>442</v>
       </c>
       <c r="E144" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F144" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G144" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H144" s="3" t="s">
         <v>53</v>
@@ -7916,7 +7919,7 @@
         <v>1</v>
       </c>
       <c r="J144" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -7924,22 +7927,22 @@
         <v>443</v>
       </c>
       <c r="B145" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C145" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D145" t="s">
         <v>444</v>
       </c>
       <c r="E145" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F145" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G145" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H145" s="3" t="s">
         <v>53</v>
@@ -7948,7 +7951,7 @@
         <v>1</v>
       </c>
       <c r="J145" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -7956,22 +7959,22 @@
         <v>445</v>
       </c>
       <c r="B146" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C146" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D146" t="s">
         <v>446</v>
       </c>
       <c r="E146" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F146" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G146" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H146" s="3" t="s">
         <v>53</v>
@@ -7980,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="J146" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -7988,22 +7991,22 @@
         <v>447</v>
       </c>
       <c r="B147" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C147" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D147" t="s">
         <v>448</v>
       </c>
       <c r="E147" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F147" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G147" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H147" s="3" t="s">
         <v>53</v>
@@ -8012,7 +8015,7 @@
         <v>1</v>
       </c>
       <c r="J147" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -8020,22 +8023,22 @@
         <v>449</v>
       </c>
       <c r="B148" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C148" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D148" t="s">
         <v>450</v>
       </c>
       <c r="E148" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F148" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G148" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H148" s="3" t="s">
         <v>53</v>
@@ -8044,7 +8047,7 @@
         <v>1</v>
       </c>
       <c r="J148" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -8052,22 +8055,22 @@
         <v>451</v>
       </c>
       <c r="B149" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C149" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D149" t="s">
         <v>452</v>
       </c>
       <c r="E149" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F149" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G149" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H149" s="3" t="s">
         <v>53</v>
@@ -8076,7 +8079,7 @@
         <v>1</v>
       </c>
       <c r="J149" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -8084,22 +8087,22 @@
         <v>453</v>
       </c>
       <c r="B150" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C150" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D150" t="s">
         <v>454</v>
       </c>
       <c r="E150" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F150" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G150" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H150" s="3" t="s">
         <v>53</v>
@@ -8108,7 +8111,7 @@
         <v>1</v>
       </c>
       <c r="J150" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -8116,22 +8119,22 @@
         <v>455</v>
       </c>
       <c r="B151" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C151" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D151" t="s">
         <v>456</v>
       </c>
       <c r="E151" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F151" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G151" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H151" s="3" t="s">
         <v>53</v>
@@ -8140,7 +8143,7 @@
         <v>1</v>
       </c>
       <c r="J151" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -8172,7 +8175,7 @@
         <v>1</v>
       </c>
       <c r="J152" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -8204,7 +8207,7 @@
         <v>1</v>
       </c>
       <c r="J153" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -8236,7 +8239,7 @@
         <v>1</v>
       </c>
       <c r="J154" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -8268,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="J155" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -8300,7 +8303,7 @@
         <v>1</v>
       </c>
       <c r="J156" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -8332,7 +8335,7 @@
         <v>1</v>
       </c>
       <c r="J157" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -8364,7 +8367,7 @@
         <v>1</v>
       </c>
       <c r="J158" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -8396,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="J159" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -8428,7 +8431,7 @@
         <v>1</v>
       </c>
       <c r="J160" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -8460,7 +8463,7 @@
         <v>1</v>
       </c>
       <c r="J161" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -8492,7 +8495,7 @@
         <v>1</v>
       </c>
       <c r="J162" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -8524,7 +8527,7 @@
         <v>1</v>
       </c>
       <c r="J163" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -8556,7 +8559,7 @@
         <v>1</v>
       </c>
       <c r="J164" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -8588,7 +8591,7 @@
         <v>1</v>
       </c>
       <c r="J165" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -8620,7 +8623,7 @@
         <v>1</v>
       </c>
       <c r="J166" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -8652,7 +8655,7 @@
         <v>1</v>
       </c>
       <c r="J167" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
@@ -8684,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="J168" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -8716,7 +8719,7 @@
         <v>1</v>
       </c>
       <c r="J169" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -8748,7 +8751,7 @@
         <v>1</v>
       </c>
       <c r="J170" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -8780,7 +8783,7 @@
         <v>1</v>
       </c>
       <c r="J171" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -8812,7 +8815,7 @@
         <v>1</v>
       </c>
       <c r="J172" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -8844,7 +8847,7 @@
         <v>1</v>
       </c>
       <c r="J173" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -8876,7 +8879,7 @@
         <v>1</v>
       </c>
       <c r="J174" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -8908,7 +8911,7 @@
         <v>1</v>
       </c>
       <c r="J175" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -8940,7 +8943,7 @@
         <v>1</v>
       </c>
       <c r="J176" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -8972,7 +8975,7 @@
         <v>1</v>
       </c>
       <c r="J177" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -9004,7 +9007,7 @@
         <v>1</v>
       </c>
       <c r="J178" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -9036,7 +9039,7 @@
         <v>1</v>
       </c>
       <c r="J179" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -9068,7 +9071,7 @@
         <v>1</v>
       </c>
       <c r="J180" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -9100,7 +9103,7 @@
         <v>1</v>
       </c>
       <c r="J181" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -9132,12 +9135,12 @@
         <v>1</v>
       </c>
       <c r="J182" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B183" t="s">
         <v>458</v>
@@ -9146,10 +9149,10 @@
         <v>459</v>
       </c>
       <c r="D183" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E183" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F183" t="s">
         <v>462</v>
@@ -9164,12 +9167,12 @@
         <v>1</v>
       </c>
       <c r="J183" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B184" t="s">
         <v>458</v>
@@ -9178,10 +9181,10 @@
         <v>459</v>
       </c>
       <c r="D184" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E184" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F184" t="s">
         <v>462</v>
@@ -9196,12 +9199,12 @@
         <v>1</v>
       </c>
       <c r="J184" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B185" t="s">
         <v>458</v>
@@ -9210,10 +9213,10 @@
         <v>459</v>
       </c>
       <c r="D185" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E185" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F185" t="s">
         <v>462</v>
@@ -9228,12 +9231,12 @@
         <v>1</v>
       </c>
       <c r="J185" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B186" t="s">
         <v>458</v>
@@ -9242,10 +9245,10 @@
         <v>459</v>
       </c>
       <c r="D186" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E186" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F186" t="s">
         <v>462</v>
@@ -9260,30 +9263,30 @@
         <v>1</v>
       </c>
       <c r="J186" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B187" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C187" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D187" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E187" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F187" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G187" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H187" s="3" t="s">
         <v>53</v>
@@ -9292,30 +9295,30 @@
         <v>1</v>
       </c>
       <c r="J187" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B188" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C188" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D188" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E188" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F188" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G188" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H188" s="3" t="s">
         <v>53</v>
@@ -9324,30 +9327,30 @@
         <v>1</v>
       </c>
       <c r="J188" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B189" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C189" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D189" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E189" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F189" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G189" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>53</v>
@@ -9356,30 +9359,30 @@
         <v>1</v>
       </c>
       <c r="J189" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B190" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C190" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D190" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E190" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F190" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G190" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H190" s="3" t="s">
         <v>53</v>
@@ -9388,30 +9391,30 @@
         <v>1</v>
       </c>
       <c r="J190" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B191" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C191" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D191" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E191" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F191" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G191" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H191" s="3" t="s">
         <v>53</v>
@@ -9420,30 +9423,30 @@
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B192" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C192" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D192" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E192" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F192" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G192" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H192" s="3" t="s">
         <v>53</v>
@@ -9452,30 +9455,30 @@
         <v>1</v>
       </c>
       <c r="J192" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B193" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C193" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D193" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E193" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F193" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G193" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>53</v>
@@ -9484,30 +9487,30 @@
         <v>1</v>
       </c>
       <c r="J193" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B194" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C194" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D194" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E194" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F194" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G194" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H194" s="3" t="s">
         <v>53</v>
@@ -9516,30 +9519,30 @@
         <v>1</v>
       </c>
       <c r="J194" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B195" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C195" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D195" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E195" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F195" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G195" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H195" s="3" t="s">
         <v>53</v>
@@ -9548,30 +9551,30 @@
         <v>1</v>
       </c>
       <c r="J195" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B196" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C196" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D196" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E196" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F196" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G196" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H196" s="3" t="s">
         <v>53</v>
@@ -9580,30 +9583,30 @@
         <v>1</v>
       </c>
       <c r="J196" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B197" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C197" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D197" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E197" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F197" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G197" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H197" s="3" t="s">
         <v>53</v>
@@ -9612,30 +9615,30 @@
         <v>1</v>
       </c>
       <c r="J197" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B198" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C198" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D198" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E198" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F198" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G198" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H198" s="3" t="s">
         <v>53</v>
@@ -9644,30 +9647,30 @@
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B199" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C199" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D199" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E199" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F199" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G199" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H199" s="3" t="s">
         <v>53</v>
@@ -9676,30 +9679,30 @@
         <v>1</v>
       </c>
       <c r="J199" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B200" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C200" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D200" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E200" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F200" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G200" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H200" s="3" t="s">
         <v>53</v>
@@ -9708,30 +9711,30 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B201" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C201" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D201" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E201" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F201" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G201" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H201" s="3" t="s">
         <v>53</v>
@@ -9740,30 +9743,30 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B202" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C202" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D202" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E202" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F202" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G202" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H202" s="3" t="s">
         <v>53</v>
@@ -9772,30 +9775,30 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B203" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C203" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D203" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E203" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F203" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G203" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H203" s="3" t="s">
         <v>53</v>
@@ -9804,30 +9807,30 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B204" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C204" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D204" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E204" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F204" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G204" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H204" s="3" t="s">
         <v>53</v>
@@ -9836,30 +9839,30 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B205" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C205" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D205" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E205" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F205" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G205" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H205" s="3" t="s">
         <v>53</v>
@@ -9868,30 +9871,30 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B206" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C206" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D206" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E206" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F206" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G206" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H206" s="3" t="s">
         <v>53</v>
@@ -9900,30 +9903,30 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B207" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C207" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D207" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E207" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F207" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G207" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H207" s="3" t="s">
         <v>53</v>
@@ -9932,30 +9935,30 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B208" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C208" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D208" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E208" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F208" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G208" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H208" s="3" t="s">
         <v>53</v>
@@ -9964,30 +9967,30 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B209" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C209" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D209" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E209" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F209" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G209" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H209" s="3" t="s">
         <v>53</v>
@@ -9996,30 +9999,30 @@
         <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B210" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C210" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D210" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E210" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F210" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G210" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H210" s="3" t="s">
         <v>53</v>
@@ -10028,30 +10031,30 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B211" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C211" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D211" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E211" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F211" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G211" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H211" s="3" t="s">
         <v>53</v>
@@ -10060,30 +10063,30 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B212" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C212" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D212" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E212" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F212" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G212" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H212" s="3" t="s">
         <v>53</v>
@@ -10092,30 +10095,30 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B213" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C213" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D213" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E213" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F213" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G213" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H213" s="3" t="s">
         <v>53</v>
@@ -10124,30 +10127,30 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B214" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C214" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D214" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E214" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F214" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G214" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H214" s="3" t="s">
         <v>53</v>
@@ -10156,30 +10159,30 @@
         <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B215" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C215" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D215" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E215" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F215" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G215" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H215" s="3" t="s">
         <v>53</v>
@@ -10188,30 +10191,30 @@
         <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B216" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C216" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D216" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E216" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F216" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G216" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H216" s="3" t="s">
         <v>53</v>
@@ -10220,30 +10223,30 @@
         <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B217" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C217" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D217" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E217" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F217" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G217" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H217" s="3" t="s">
         <v>53</v>
@@ -10252,30 +10255,30 @@
         <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B218" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C218" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D218" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E218" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F218" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G218" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H218" s="3" t="s">
         <v>53</v>
@@ -10284,30 +10287,30 @@
         <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>410</v>
+        <v>554</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B219" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C219" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D219" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E219" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F219" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G219" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H219" s="3" t="s">
         <v>53</v>
@@ -10316,7 +10319,7 @@
         <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
@@ -10324,10 +10327,10 @@
         <v>702</v>
       </c>
       <c r="B220" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C220" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D220" t="s">
         <v>703</v>
@@ -10336,7 +10339,7 @@
         <v>704</v>
       </c>
       <c r="F220" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G220" t="s">
         <v>705</v>
@@ -10348,7 +10351,7 @@
         <v>1</v>
       </c>
       <c r="J220" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -10356,10 +10359,10 @@
         <v>706</v>
       </c>
       <c r="B221" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C221" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D221" t="s">
         <v>707</v>
@@ -10368,7 +10371,7 @@
         <v>708</v>
       </c>
       <c r="F221" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G221" t="s">
         <v>709</v>
@@ -10380,7 +10383,7 @@
         <v>1</v>
       </c>
       <c r="J221" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
@@ -10412,7 +10415,7 @@
         <v>1</v>
       </c>
       <c r="J222" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
@@ -10444,7 +10447,7 @@
         <v>1</v>
       </c>
       <c r="J223" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
@@ -10476,7 +10479,7 @@
         <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -10508,7 +10511,7 @@
         <v>1</v>
       </c>
       <c r="J225" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
@@ -10540,7 +10543,7 @@
         <v>1</v>
       </c>
       <c r="J226" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
@@ -10572,7 +10575,7 @@
         <v>1</v>
       </c>
       <c r="J227" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
@@ -10604,7 +10607,7 @@
         <v>1</v>
       </c>
       <c r="J228" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
@@ -10636,7 +10639,7 @@
         <v>1</v>
       </c>
       <c r="J229" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
@@ -10668,7 +10671,7 @@
         <v>1</v>
       </c>
       <c r="J230" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
@@ -10700,7 +10703,7 @@
         <v>1</v>
       </c>
       <c r="J231" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
@@ -10732,7 +10735,7 @@
         <v>1</v>
       </c>
       <c r="J232" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
@@ -10764,7 +10767,7 @@
         <v>1</v>
       </c>
       <c r="J233" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
@@ -10796,7 +10799,7 @@
         <v>1</v>
       </c>
       <c r="J234" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
@@ -10828,7 +10831,7 @@
         <v>1</v>
       </c>
       <c r="J235" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
@@ -10860,7 +10863,7 @@
         <v>1</v>
       </c>
       <c r="J236" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
@@ -10892,12 +10895,12 @@
         <v>1</v>
       </c>
       <c r="J237" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B238" t="s">
         <v>711</v>
@@ -10906,7 +10909,7 @@
         <v>712</v>
       </c>
       <c r="D238" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E238" t="s">
         <v>714</v>
@@ -10924,12 +10927,12 @@
         <v>1</v>
       </c>
       <c r="J238" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B239" t="s">
         <v>711</v>
@@ -10938,7 +10941,7 @@
         <v>712</v>
       </c>
       <c r="D239" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E239" t="s">
         <v>714</v>
@@ -10956,12 +10959,12 @@
         <v>1</v>
       </c>
       <c r="J239" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B240" t="s">
         <v>711</v>
@@ -10970,7 +10973,7 @@
         <v>712</v>
       </c>
       <c r="D240" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E240" t="s">
         <v>714</v>
@@ -10988,12 +10991,12 @@
         <v>1</v>
       </c>
       <c r="J240" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B241" t="s">
         <v>711</v>
@@ -11002,7 +11005,7 @@
         <v>712</v>
       </c>
       <c r="D241" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E241" t="s">
         <v>714</v>
@@ -11020,12 +11023,12 @@
         <v>1</v>
       </c>
       <c r="J241" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B242" t="s">
         <v>711</v>
@@ -11034,7 +11037,7 @@
         <v>712</v>
       </c>
       <c r="D242" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E242" t="s">
         <v>714</v>
@@ -11052,12 +11055,12 @@
         <v>1</v>
       </c>
       <c r="J242" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B243" t="s">
         <v>711</v>
@@ -11066,7 +11069,7 @@
         <v>712</v>
       </c>
       <c r="D243" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E243" t="s">
         <v>714</v>
@@ -11084,12 +11087,12 @@
         <v>1</v>
       </c>
       <c r="J243" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B244" t="s">
         <v>711</v>
@@ -11098,7 +11101,7 @@
         <v>712</v>
       </c>
       <c r="D244" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E244" t="s">
         <v>714</v>
@@ -11116,12 +11119,12 @@
         <v>1</v>
       </c>
       <c r="J244" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B245" t="s">
         <v>711</v>
@@ -11130,7 +11133,7 @@
         <v>712</v>
       </c>
       <c r="D245" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E245" t="s">
         <v>714</v>
@@ -11148,12 +11151,12 @@
         <v>1</v>
       </c>
       <c r="J245" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B246" t="s">
         <v>711</v>
@@ -11162,7 +11165,7 @@
         <v>712</v>
       </c>
       <c r="D246" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E246" t="s">
         <v>714</v>
@@ -11180,30 +11183,30 @@
         <v>1</v>
       </c>
       <c r="J246" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B247" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C247" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D247" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E247" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F247" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G247" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H247" s="3" t="s">
         <v>53</v>
@@ -11212,31 +11215,31 @@
         <v>1</v>
       </c>
       <c r="J247" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>773</v>
+      </c>
+      <c r="B248" t="s">
+        <v>767</v>
+      </c>
+      <c r="C248" t="s">
+        <v>768</v>
+      </c>
+      <c r="D248" t="s">
+        <v>774</v>
+      </c>
+      <c r="E248" t="s">
+        <v>770</v>
+      </c>
+      <c r="F248" t="s">
+        <v>771</v>
+      </c>
+      <c r="G248" t="s">
         <v>772</v>
       </c>
-      <c r="B248" t="s">
-        <v>766</v>
-      </c>
-      <c r="C248" t="s">
-        <v>767</v>
-      </c>
-      <c r="D248" t="s">
-        <v>773</v>
-      </c>
-      <c r="E248" t="s">
-        <v>769</v>
-      </c>
-      <c r="F248" t="s">
-        <v>770</v>
-      </c>
-      <c r="G248" t="s">
-        <v>771</v>
-      </c>
       <c r="H248" s="3" t="s">
         <v>53</v>
       </c>
@@ -11244,30 +11247,30 @@
         <v>1</v>
       </c>
       <c r="J248" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B249" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C249" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D249" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E249" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F249" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G249" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H249" s="3" t="s">
         <v>53</v>
@@ -11276,30 +11279,30 @@
         <v>1</v>
       </c>
       <c r="J249" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B250" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C250" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D250" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E250" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F250" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G250" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H250" s="3" t="s">
         <v>53</v>
@@ -11308,30 +11311,30 @@
         <v>1</v>
       </c>
       <c r="J250" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B251" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C251" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D251" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E251" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F251" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G251" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H251" s="3" t="s">
         <v>53</v>
@@ -11340,30 +11343,30 @@
         <v>1</v>
       </c>
       <c r="J251" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B252" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C252" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D252" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E252" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F252" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G252" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H252" s="3" t="s">
         <v>53</v>
@@ -11372,30 +11375,30 @@
         <v>1</v>
       </c>
       <c r="J252" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B253" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C253" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D253" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E253" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F253" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G253" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H253" s="3" t="s">
         <v>53</v>
@@ -11404,30 +11407,30 @@
         <v>1</v>
       </c>
       <c r="J253" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B254" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C254" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D254" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E254" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F254" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G254" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H254" s="3" t="s">
         <v>53</v>
@@ -11436,30 +11439,30 @@
         <v>1</v>
       </c>
       <c r="J254" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B255" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C255" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D255" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E255" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F255" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G255" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H255" s="3" t="s">
         <v>53</v>
@@ -11468,30 +11471,30 @@
         <v>1</v>
       </c>
       <c r="J255" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B256" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C256" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D256" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E256" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F256" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G256" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H256" s="3" t="s">
         <v>53</v>
@@ -11500,30 +11503,30 @@
         <v>1</v>
       </c>
       <c r="J256" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B257" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C257" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D257" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E257" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F257" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G257" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H257" s="3" t="s">
         <v>53</v>
@@ -11532,30 +11535,30 @@
         <v>1</v>
       </c>
       <c r="J257" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B258" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C258" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D258" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E258" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F258" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G258" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>53</v>
@@ -11564,30 +11567,30 @@
         <v>1</v>
       </c>
       <c r="J258" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B259" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C259" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D259" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E259" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F259" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G259" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>53</v>
@@ -11596,30 +11599,30 @@
         <v>1</v>
       </c>
       <c r="J259" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B260" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C260" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D260" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E260" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F260" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G260" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>53</v>
@@ -11628,30 +11631,30 @@
         <v>1</v>
       </c>
       <c r="J260" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B261" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C261" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D261" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E261" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F261" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G261" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>53</v>
@@ -11660,30 +11663,30 @@
         <v>1</v>
       </c>
       <c r="J261" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B262" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C262" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D262" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E262" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F262" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G262" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H262" s="3" t="s">
         <v>53</v>
@@ -11692,30 +11695,30 @@
         <v>1</v>
       </c>
       <c r="J262" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B263" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C263" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D263" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E263" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F263" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G263" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H263" s="3" t="s">
         <v>53</v>
@@ -11724,30 +11727,30 @@
         <v>1</v>
       </c>
       <c r="J263" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B264" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C264" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D264" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E264" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F264" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G264" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H264" s="3" t="s">
         <v>53</v>
@@ -11756,30 +11759,30 @@
         <v>1</v>
       </c>
       <c r="J264" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B265" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C265" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D265" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E265" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F265" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G265" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H265" s="3" t="s">
         <v>53</v>
@@ -11788,30 +11791,30 @@
         <v>1</v>
       </c>
       <c r="J265" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B266" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C266" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D266" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E266" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F266" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G266" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H266" s="3" t="s">
         <v>53</v>
@@ -11820,30 +11823,30 @@
         <v>1</v>
       </c>
       <c r="J266" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B267" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C267" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D267" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E267" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F267" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G267" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H267" s="3" t="s">
         <v>53</v>
@@ -11852,30 +11855,30 @@
         <v>1</v>
       </c>
       <c r="J267" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B268" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C268" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D268" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E268" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F268" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G268" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H268" s="3" t="s">
         <v>53</v>
@@ -11884,30 +11887,30 @@
         <v>1</v>
       </c>
       <c r="J268" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B269" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C269" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D269" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E269" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F269" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G269" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H269" s="3" t="s">
         <v>53</v>
@@ -11916,30 +11919,30 @@
         <v>1</v>
       </c>
       <c r="J269" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B270" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C270" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D270" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E270" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F270" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G270" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H270" s="3" t="s">
         <v>53</v>
@@ -11948,30 +11951,30 @@
         <v>1</v>
       </c>
       <c r="J270" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B271" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C271" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D271" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E271" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F271" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G271" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H271" s="3" t="s">
         <v>53</v>
@@ -11980,30 +11983,30 @@
         <v>1</v>
       </c>
       <c r="J271" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B272" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C272" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D272" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E272" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F272" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G272" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H272" s="3" t="s">
         <v>53</v>
@@ -12012,31 +12015,31 @@
         <v>1</v>
       </c>
       <c r="J272" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>828</v>
+      </c>
+      <c r="B273" t="s">
+        <v>822</v>
+      </c>
+      <c r="C273" t="s">
+        <v>823</v>
+      </c>
+      <c r="D273" t="s">
+        <v>829</v>
+      </c>
+      <c r="E273" t="s">
+        <v>825</v>
+      </c>
+      <c r="F273" t="s">
+        <v>826</v>
+      </c>
+      <c r="G273" t="s">
         <v>827</v>
       </c>
-      <c r="B273" t="s">
-        <v>821</v>
-      </c>
-      <c r="C273" t="s">
-        <v>822</v>
-      </c>
-      <c r="D273" t="s">
-        <v>828</v>
-      </c>
-      <c r="E273" t="s">
-        <v>824</v>
-      </c>
-      <c r="F273" t="s">
-        <v>825</v>
-      </c>
-      <c r="G273" t="s">
-        <v>826</v>
-      </c>
       <c r="H273" s="3" t="s">
         <v>53</v>
       </c>
@@ -12044,30 +12047,30 @@
         <v>1</v>
       </c>
       <c r="J273" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B274" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C274" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D274" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E274" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F274" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G274" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H274" s="3" t="s">
         <v>53</v>
@@ -12076,30 +12079,30 @@
         <v>1</v>
       </c>
       <c r="J274" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B275" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C275" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D275" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E275" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F275" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G275" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H275" s="3" t="s">
         <v>53</v>
@@ -12108,30 +12111,30 @@
         <v>1</v>
       </c>
       <c r="J275" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B276" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C276" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D276" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E276" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F276" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G276" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H276" s="3" t="s">
         <v>53</v>
@@ -12140,30 +12143,30 @@
         <v>1</v>
       </c>
       <c r="J276" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B277" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C277" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D277" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E277" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F277" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G277" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H277" s="3" t="s">
         <v>53</v>
@@ -12172,30 +12175,30 @@
         <v>1</v>
       </c>
       <c r="J277" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B278" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C278" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D278" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E278" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F278" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G278" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H278" s="3" t="s">
         <v>53</v>
@@ -12204,30 +12207,30 @@
         <v>1</v>
       </c>
       <c r="J278" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B279" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C279" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D279" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E279" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F279" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G279" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H279" s="3" t="s">
         <v>53</v>
@@ -12236,30 +12239,30 @@
         <v>1</v>
       </c>
       <c r="J279" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B280" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C280" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D280" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E280" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F280" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G280" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H280" s="3" t="s">
         <v>53</v>
@@ -12268,30 +12271,30 @@
         <v>1</v>
       </c>
       <c r="J280" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B281" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C281" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D281" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="E281" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F281" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G281" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H281" s="3" t="s">
         <v>53</v>
@@ -12300,30 +12303,30 @@
         <v>1</v>
       </c>
       <c r="J281" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B282" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C282" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D282" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E282" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F282" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G282" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H282" s="3" t="s">
         <v>53</v>
@@ -12332,30 +12335,30 @@
         <v>1</v>
       </c>
       <c r="J282" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B283" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C283" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D283" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E283" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F283" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G283" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H283" s="3" t="s">
         <v>53</v>
@@ -12364,30 +12367,30 @@
         <v>1</v>
       </c>
       <c r="J283" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B284" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C284" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D284" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E284" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F284" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G284" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H284" s="3" t="s">
         <v>53</v>
@@ -12396,30 +12399,30 @@
         <v>1</v>
       </c>
       <c r="J284" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B285" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C285" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D285" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E285" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F285" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G285" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H285" s="3" t="s">
         <v>53</v>
@@ -12428,30 +12431,30 @@
         <v>1</v>
       </c>
       <c r="J285" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B286" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C286" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D286" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E286" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F286" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G286" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H286" s="3" t="s">
         <v>53</v>
@@ -12460,30 +12463,30 @@
         <v>1</v>
       </c>
       <c r="J286" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B287" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C287" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D287" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E287" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F287" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G287" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H287" s="3" t="s">
         <v>53</v>
@@ -12492,30 +12495,30 @@
         <v>1</v>
       </c>
       <c r="J287" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B288" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C288" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D288" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E288" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F288" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G288" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H288" s="3" t="s">
         <v>53</v>
@@ -12524,30 +12527,30 @@
         <v>1</v>
       </c>
       <c r="J288" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B289" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C289" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D289" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E289" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F289" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G289" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H289" s="3" t="s">
         <v>53</v>
@@ -12556,30 +12559,30 @@
         <v>1</v>
       </c>
       <c r="J289" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B290" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C290" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D290" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E290" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F290" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G290" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H290" s="3" t="s">
         <v>53</v>
@@ -12588,30 +12591,30 @@
         <v>1</v>
       </c>
       <c r="J290" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B291" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C291" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D291" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E291" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F291" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G291" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H291" s="3" t="s">
         <v>53</v>
@@ -12620,30 +12623,30 @@
         <v>1</v>
       </c>
       <c r="J291" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B292" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C292" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D292" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E292" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F292" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G292" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H292" s="3" t="s">
         <v>53</v>
@@ -12652,30 +12655,30 @@
         <v>1</v>
       </c>
       <c r="J292" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B293" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C293" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D293" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E293" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F293" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G293" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H293" s="3" t="s">
         <v>53</v>
@@ -12684,30 +12687,30 @@
         <v>1</v>
       </c>
       <c r="J293" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B294" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C294" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D294" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E294" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F294" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G294" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H294" s="3" t="s">
         <v>53</v>
@@ -12716,30 +12719,30 @@
         <v>1</v>
       </c>
       <c r="J294" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B295" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C295" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D295" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E295" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F295" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G295" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H295" s="3" t="s">
         <v>53</v>
@@ -12748,30 +12751,30 @@
         <v>1</v>
       </c>
       <c r="J295" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B296" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C296" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D296" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E296" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F296" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G296" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H296" s="3" t="s">
         <v>53</v>
@@ -12780,30 +12783,30 @@
         <v>1</v>
       </c>
       <c r="J296" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B297" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C297" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D297" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E297" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F297" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G297" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H297" s="3" t="s">
         <v>53</v>
@@ -12812,30 +12815,30 @@
         <v>1</v>
       </c>
       <c r="J297" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B298" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C298" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D298" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E298" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F298" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G298" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H298" s="3" t="s">
         <v>53</v>
@@ -12844,30 +12847,30 @@
         <v>1</v>
       </c>
       <c r="J298" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B299" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C299" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D299" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E299" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F299" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G299" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H299" s="3" t="s">
         <v>53</v>
@@ -12876,30 +12879,30 @@
         <v>1</v>
       </c>
       <c r="J299" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B300" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C300" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D300" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E300" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F300" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G300" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H300" s="3" t="s">
         <v>53</v>
@@ -12908,30 +12911,30 @@
         <v>1</v>
       </c>
       <c r="J300" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B301" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C301" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D301" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E301" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F301" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G301" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H301" s="3" t="s">
         <v>53</v>
@@ -12940,7 +12943,7 @@
         <v>1</v>
       </c>
       <c r="J301" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
     </row>
   </sheetData>
